--- a/src/attributions/attributions_saliency_traj_191.xlsx
+++ b/src/attributions/attributions_saliency_traj_191.xlsx
@@ -999,6261 +999,6261 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9.649659477872774e-05</v>
+        <v>4.618642321929656e-07</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006523407646454871</v>
+        <v>5.111296559334733e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001160809115390293</v>
+        <v>7.332051836783648e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002433180634398013</v>
+        <v>4.809655251847289e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>8.286144293379039e-05</v>
+        <v>5.618460363621125e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008541257120668888</v>
+        <v>8.019918823265471e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.206101483665407e-05</v>
+        <v>1.370485279039713e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003400545683689415</v>
+        <v>1.297752419304743e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.865363684482872e-05</v>
+        <v>1.877383169812674e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.161404285696335e-05</v>
+        <v>2.778388079605065e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005950130871497095</v>
+        <v>7.575271865789546e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001064019888872281</v>
+        <v>2.465826810293947e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0002368062705500051</v>
+        <v>2.622473857627483e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001594454952282831</v>
+        <v>7.290163921425119e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0005994983366690576</v>
+        <v>1.04857754195109e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>6.340446998365223e-05</v>
+        <v>9.742723250383278e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002889399183914065</v>
+        <v>1.100337499337911e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.554033588035963e-06</v>
+        <v>2.897888634834089e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.727095438283868e-05</v>
+        <v>9.619950560590951e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>5.254672942101024e-05</v>
+        <v>1.087315467884764e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.504926694906317e-05</v>
+        <v>7.810824058651633e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0001241297431988642</v>
+        <v>3.980486781074433e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>8.233147673308849e-05</v>
+        <v>1.10358291749435e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>7.061909855110571e-05</v>
+        <v>2.485484856151743e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.217719030450098e-06</v>
+        <v>2.245620862595388e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.922329829540104e-06</v>
+        <v>2.027273467319901e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.311141750193201e-05</v>
+        <v>6.416537701170455e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.496640379627934e-05</v>
+        <v>3.03229990095133e-06</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.525195279507898e-05</v>
+        <v>5.766498816228705e-07</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.162613085005432e-05</v>
+        <v>4.695596658166323e-07</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.829999332083389e-05</v>
+        <v>2.8307563297858e-06</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.779160397243686e-05</v>
+        <v>4.862431524088606e-06</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.503231710055843e-05</v>
+        <v>1.696001049822371e-06</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.000107282045064494</v>
+        <v>2.194236685681972e-06</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.643264790298417e-05</v>
+        <v>5.346315447241068e-06</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.99083219235763e-05</v>
+        <v>2.697813215490896e-06</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0001125852650147863</v>
+        <v>6.212283096829196e-07</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.596687383833341e-05</v>
+        <v>9.047868729794573e-07</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.367433211882599e-05</v>
+        <v>1.258908355339372e-06</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.376914022141136e-06</v>
+        <v>1.354651885776548e-06</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.178032627853099e-05</v>
+        <v>1.815604264265858e-06</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0001566677528899163</v>
+        <v>2.991667315654922e-06</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.564327926142141e-07</v>
+        <v>2.050670957487455e-07</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0001116431085392833</v>
+        <v>3.69846384273842e-06</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.556066647230182e-05</v>
+        <v>2.109748493239749e-06</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.176011937786825e-05</v>
+        <v>8.696908935235115e-07</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.0003558892931323498</v>
+        <v>1.358689314656658e-05</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.338276868220419e-06</v>
+        <v>2.398074684606399e-06</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.834822463337332e-05</v>
+        <v>1.856186145232641e-06</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0001757422141963616</v>
+        <v>3.565958877516096e-06</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0006031141965650022</v>
+        <v>1.017754766508006e-05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.000108128268038854</v>
+        <v>1.353502057099831e-07</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.295246981200762e-05</v>
+        <v>1.386605731568125e-06</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.056403359863907e-05</v>
+        <v>5.960301336926932e-07</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.636441296199337e-05</v>
+        <v>5.837759999849368e-07</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0001864517398644239</v>
+        <v>7.030265805951785e-06</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0001195664517581463</v>
+        <v>3.32537638314534e-07</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0001155819045379758</v>
+        <v>6.701930033159442e-07</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0001242953003384173</v>
+        <v>6.301058874669252e-07</v>
       </c>
       <c r="BH2" t="n">
-        <v>7.510821160394698e-05</v>
+        <v>2.217545443272684e-06</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.222857256128918e-05</v>
+        <v>1.612498181202682e-06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2.804678297252394e-05</v>
+        <v>3.345647314745293e-08</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.365908949286677e-05</v>
+        <v>2.927521109086229e-06</v>
       </c>
       <c r="BL2" t="n">
-        <v>4.886844908469357e-05</v>
+        <v>1.558802750878385e-06</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0001864799414761364</v>
+        <v>2.628667289172881e-06</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.610616088029929e-05</v>
+        <v>1.65341214142245e-06</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.676423511933535e-05</v>
+        <v>4.479074959817808e-07</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.162800804711878e-05</v>
+        <v>2.598694209154928e-06</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.256059037288651e-05</v>
+        <v>2.415406186173641e-07</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.322305979556404e-05</v>
+        <v>1.69607892530621e-06</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.241709732217714e-05</v>
+        <v>1.602301836101105e-06</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.450264820363373e-05</v>
+        <v>4.864502045620611e-08</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.465994500904344e-06</v>
+        <v>9.733957995194942e-08</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0002066009619738907</v>
+        <v>5.949513251835015e-06</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.803660365520045e-05</v>
+        <v>1.636173578845046e-07</v>
       </c>
       <c r="BX2" t="n">
-        <v>8.333592995768413e-05</v>
+        <v>1.205309786200814e-06</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0001048361154971644</v>
+        <v>2.207821125921328e-08</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0002755514578893781</v>
+        <v>6.712547474307939e-06</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.342523657716811e-06</v>
+        <v>1.6790552308521e-06</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.0001181311527034268</v>
+        <v>2.072769348160364e-06</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.37773474509595e-06</v>
+        <v>1.422905825165799e-06</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.702792724245228e-05</v>
+        <v>7.039910769890412e-07</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0001052208899636753</v>
+        <v>2.366190983593697e-06</v>
       </c>
       <c r="CF2" t="n">
-        <v>7.729668141109869e-06</v>
+        <v>4.256311854078376e-07</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.189196311519481e-05</v>
+        <v>2.435026544844732e-07</v>
       </c>
       <c r="CH2" t="n">
-        <v>3.563338395906612e-05</v>
+        <v>5.561432772083208e-07</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0001088598219212145</v>
+        <v>2.804214091156609e-06</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.186209192383103e-05</v>
+        <v>1.714724021439906e-06</v>
       </c>
       <c r="CK2" t="n">
-        <v>5.972565850242972e-05</v>
+        <v>2.313737468284671e-07</v>
       </c>
       <c r="CL2" t="n">
-        <v>9.727743417897727e-06</v>
+        <v>7.598378601869626e-07</v>
       </c>
       <c r="CM2" t="n">
-        <v>8.093908400041983e-05</v>
+        <v>3.082085413552704e-06</v>
       </c>
       <c r="CN2" t="n">
-        <v>9.035924449563026e-06</v>
+        <v>3.947354343836196e-06</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.040174356603529e-05</v>
+        <v>7.490501729989774e-08</v>
       </c>
       <c r="CP2" t="n">
-        <v>3.712339093908668e-05</v>
+        <v>2.740324362093816e-06</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.125035411561839e-05</v>
+        <v>1.320944079452602e-06</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.0001109745135181583</v>
+        <v>4.360590082796989e-06</v>
       </c>
       <c r="CS2" t="n">
-        <v>5.046647856943309e-05</v>
+        <v>1.009542984320433e-06</v>
       </c>
       <c r="CT2" t="n">
-        <v>6.666334229521453e-05</v>
+        <v>2.003732788580237e-06</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.0001172470292658545</v>
+        <v>1.862832590404651e-07</v>
       </c>
       <c r="CV2" t="n">
-        <v>3.180700514349155e-05</v>
+        <v>1.282012817682698e-06</v>
       </c>
       <c r="CW2" t="n">
-        <v>9.802423301152885e-05</v>
+        <v>2.335452336410526e-06</v>
       </c>
       <c r="CX2" t="n">
-        <v>2.584329195087776e-06</v>
+        <v>3.305709128653689e-07</v>
       </c>
       <c r="CY2" t="n">
-        <v>3.680312511278316e-05</v>
+        <v>5.659828161697078e-07</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.543776281527244e-05</v>
+        <v>5.30042711943679e-07</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0001240577548742294</v>
+        <v>2.620659188323771e-06</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.61953539645765e-06</v>
+        <v>5.913034328841604e-07</v>
       </c>
       <c r="DC2" t="n">
-        <v>8.573402010370046e-05</v>
+        <v>2.274732935347856e-07</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.370911508682184e-05</v>
+        <v>2.70128595047936e-07</v>
       </c>
       <c r="DE2" t="n">
-        <v>9.88856190815568e-05</v>
+        <v>1.600291398062836e-06</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.0003036843845620751</v>
+        <v>5.78013668928179e-07</v>
       </c>
       <c r="DG2" t="n">
-        <v>5.850994057254866e-06</v>
+        <v>2.242432856291998e-06</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.000117006893560756</v>
+        <v>1.361703425573069e-06</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0003353479842189699</v>
+        <v>2.782251726785034e-07</v>
       </c>
       <c r="DJ2" t="n">
-        <v>4.771474414155819e-05</v>
+        <v>6.981082947277173e-07</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.867945244768634e-05</v>
+        <v>2.970088644360658e-06</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.0001299573050346226</v>
+        <v>6.926645710336743e-07</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0001971669553313404</v>
+        <v>1.860004431364359e-06</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.029596569424029e-05</v>
+        <v>1.347883767266467e-06</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0001549712906125933</v>
+        <v>1.175210854853503e-06</v>
       </c>
       <c r="DP2" t="n">
-        <v>4.668341352953576e-05</v>
+        <v>8.291760309475649e-07</v>
       </c>
       <c r="DQ2" t="n">
-        <v>2.607762689876836e-05</v>
+        <v>2.329092239961028e-06</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.319565000012517e-05</v>
+        <v>1.33452192585537e-06</v>
       </c>
       <c r="DS2" t="n">
-        <v>6.599166954401881e-05</v>
+        <v>2.898600541811902e-06</v>
       </c>
       <c r="DT2" t="n">
-        <v>6.98715666658245e-05</v>
+        <v>4.341196131463221e-07</v>
       </c>
       <c r="DU2" t="n">
-        <v>4.985290797776543e-05</v>
+        <v>2.818617304001236e-06</v>
       </c>
       <c r="DV2" t="n">
-        <v>2.250487159471959e-05</v>
+        <v>8.096241117527825e-07</v>
       </c>
       <c r="DW2" t="n">
-        <v>1.657813118072227e-05</v>
+        <v>6.068294311489808e-08</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.381782390642911e-05</v>
+        <v>9.871755537460558e-07</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.823393389116973e-06</v>
+        <v>6.38194364910305e-07</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.111269375542179e-05</v>
+        <v>3.114547325822059e-06</v>
       </c>
       <c r="EA2" t="n">
-        <v>3.041593663510866e-05</v>
+        <v>9.978949719879893e-07</v>
       </c>
       <c r="EB2" t="n">
-        <v>7.142144750105217e-05</v>
+        <v>2.948738256236538e-06</v>
       </c>
       <c r="EC2" t="n">
-        <v>8.139446435961872e-06</v>
+        <v>2.484500214450236e-07</v>
       </c>
       <c r="ED2" t="n">
-        <v>5.574019087362103e-05</v>
+        <v>1.281815258380448e-07</v>
       </c>
       <c r="EE2" t="n">
-        <v>8.405882545048371e-05</v>
+        <v>9.248022934116307e-07</v>
       </c>
       <c r="EF2" t="n">
-        <v>3.99458731408231e-05</v>
+        <v>4.068736103590709e-08</v>
       </c>
       <c r="EG2" t="n">
-        <v>3.674261461128481e-05</v>
+        <v>1.710046035441337e-06</v>
       </c>
       <c r="EH2" t="n">
-        <v>2.517655775591265e-05</v>
+        <v>6.12913538589055e-07</v>
       </c>
       <c r="EI2" t="n">
-        <v>1.617284397070762e-05</v>
+        <v>1.948631336290418e-07</v>
       </c>
       <c r="EJ2" t="n">
-        <v>5.664823402184993e-05</v>
+        <v>1.943616183552876e-07</v>
       </c>
       <c r="EK2" t="n">
-        <v>8.538334077456966e-05</v>
+        <v>4.431095135259966e-07</v>
       </c>
       <c r="EL2" t="n">
-        <v>2.634742668305989e-05</v>
+        <v>2.671052357072767e-08</v>
       </c>
       <c r="EM2" t="n">
-        <v>4.480202187551185e-05</v>
+        <v>3.492476992050797e-07</v>
       </c>
       <c r="EN2" t="n">
-        <v>4.00997196265962e-05</v>
+        <v>1.409109131600417e-06</v>
       </c>
       <c r="EO2" t="n">
-        <v>4.221372364554554e-05</v>
+        <v>1.77274523593951e-06</v>
       </c>
       <c r="EP2" t="n">
-        <v>2.946990207419731e-05</v>
+        <v>1.890635530799045e-06</v>
       </c>
       <c r="EQ2" t="n">
-        <v>5.033891648054123e-05</v>
+        <v>2.629877826620941e-06</v>
       </c>
       <c r="ER2" t="n">
-        <v>2.423093246761709e-05</v>
+        <v>2.536042302381247e-06</v>
       </c>
       <c r="ES2" t="n">
-        <v>8.502007403876632e-05</v>
+        <v>1.029891791404225e-06</v>
       </c>
       <c r="ET2" t="n">
-        <v>1.984036316571292e-05</v>
+        <v>6.917742325640575e-07</v>
       </c>
       <c r="EU2" t="n">
-        <v>1.588226587045938e-05</v>
+        <v>2.433082045172341e-06</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0001746327907312661</v>
+        <v>5.930032216383552e-07</v>
       </c>
       <c r="EW2" t="n">
-        <v>2.86143331322819e-05</v>
+        <v>1.5138758158173e-07</v>
       </c>
       <c r="EX2" t="n">
-        <v>2.239261630165856e-05</v>
+        <v>1.304255306422419e-06</v>
       </c>
       <c r="EY2" t="n">
-        <v>7.445939991157502e-05</v>
+        <v>2.447495489832363e-06</v>
       </c>
       <c r="EZ2" t="n">
-        <v>1.770843482518103e-05</v>
+        <v>2.708686110963754e-07</v>
       </c>
       <c r="FA2" t="n">
-        <v>1.554909613332711e-05</v>
+        <v>4.578449193104461e-07</v>
       </c>
       <c r="FB2" t="n">
-        <v>2.609116381790955e-05</v>
+        <v>1.953401351784123e-08</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0001157530350610614</v>
+        <v>2.606299631224829e-06</v>
       </c>
       <c r="FD2" t="n">
-        <v>2.328089794900734e-05</v>
+        <v>2.250460966024548e-06</v>
       </c>
       <c r="FE2" t="n">
-        <v>6.908333307364956e-05</v>
+        <v>7.397453316571045e-08</v>
       </c>
       <c r="FF2" t="n">
-        <v>2.201764436904341e-05</v>
+        <v>1.111133087761118e-07</v>
       </c>
       <c r="FG2" t="n">
-        <v>2.029709685302805e-05</v>
+        <v>2.875140125979669e-07</v>
       </c>
       <c r="FH2" t="n">
-        <v>4.149604137637652e-06</v>
+        <v>3.314920377306407e-06</v>
       </c>
       <c r="FI2" t="n">
-        <v>1.549372973386198e-05</v>
+        <v>8.497889893988031e-07</v>
       </c>
       <c r="FJ2" t="n">
-        <v>4.167703082202934e-05</v>
+        <v>2.841302375600208e-06</v>
       </c>
       <c r="FK2" t="n">
-        <v>4.63211108581163e-05</v>
+        <v>1.96735845747753e-06</v>
       </c>
       <c r="FL2" t="n">
-        <v>8.692545816302299e-05</v>
+        <v>6.116660529187357e-07</v>
       </c>
       <c r="FM2" t="n">
-        <v>8.507246093358845e-05</v>
+        <v>1.547940883028787e-06</v>
       </c>
       <c r="FN2" t="n">
-        <v>2.92389522655867e-05</v>
+        <v>1.755883772602829e-06</v>
       </c>
       <c r="FO2" t="n">
-        <v>4.057127080159262e-05</v>
+        <v>7.824638714737375e-09</v>
       </c>
       <c r="FP2" t="n">
-        <v>3.705603376147337e-05</v>
+        <v>4.021589177227725e-07</v>
       </c>
       <c r="FQ2" t="n">
-        <v>1.659281224419829e-05</v>
+        <v>4.859266027779086e-06</v>
       </c>
       <c r="FR2" t="n">
-        <v>2.836095518432558e-07</v>
+        <v>1.011574795484194e-06</v>
       </c>
       <c r="FS2" t="n">
-        <v>8.497751696268097e-05</v>
+        <v>6.2733051890973e-06</v>
       </c>
       <c r="FT2" t="n">
-        <v>3.55516021954827e-06</v>
+        <v>5.785465191365802e-07</v>
       </c>
       <c r="FU2" t="n">
-        <v>5.975515159661882e-05</v>
+        <v>7.901481694716495e-06</v>
       </c>
       <c r="FV2" t="n">
-        <v>7.912010187283158e-05</v>
+        <v>5.955924279987812e-06</v>
       </c>
       <c r="FW2" t="n">
-        <v>8.271585102193058e-06</v>
+        <v>8.954276040640252e-07</v>
       </c>
       <c r="FX2" t="n">
-        <v>3.35486292897258e-05</v>
+        <v>8.793818437879963e-07</v>
       </c>
       <c r="FY2" t="n">
-        <v>6.947971996851265e-05</v>
+        <v>6.902689051457855e-07</v>
       </c>
       <c r="FZ2" t="n">
-        <v>1.175855459223385e-06</v>
+        <v>3.770915384393447e-07</v>
       </c>
       <c r="GA2" t="n">
-        <v>1.201007944473531e-05</v>
+        <v>1.622798180278551e-07</v>
       </c>
       <c r="GB2" t="n">
-        <v>4.155794158577919e-05</v>
+        <v>2.184102413593791e-06</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.0002787032281048596</v>
+        <v>2.715178652579198e-06</v>
       </c>
       <c r="GD2" t="n">
-        <v>8.657536818645895e-05</v>
+        <v>9.45328224588593e-07</v>
       </c>
       <c r="GE2" t="n">
-        <v>7.041244680294767e-05</v>
+        <v>3.048097823921125e-06</v>
       </c>
       <c r="GF2" t="n">
-        <v>2.646396751515567e-06</v>
+        <v>4.689391346346383e-07</v>
       </c>
       <c r="GG2" t="n">
-        <v>3.818458935711533e-05</v>
+        <v>1.489653982389427e-06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0004709749191533774</v>
+        <v>4.852193408351468e-13</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004207930061966181</v>
+        <v>5.502564549841882e-13</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004205753502901644</v>
+        <v>9.078371734916324e-13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001703456393443048</v>
+        <v>8.294609031740674e-13</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001225308049470186</v>
+        <v>1.065120010961852e-13</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001650947378948331</v>
+        <v>7.45778167953598e-13</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005577674019150436</v>
+        <v>4.510481072840522e-13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008331997669301927</v>
+        <v>3.895673388910892e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000771503197029233</v>
+        <v>9.391816751386228e-13</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001627511228434741</v>
+        <v>5.702916437699823e-13</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004547774326056242</v>
+        <v>1.816312671012316e-13</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004149626474827528</v>
+        <v>1.184568285475529e-12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006101630278863013</v>
+        <v>1.492641730702071e-12</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000721229356713593</v>
+        <v>2.870670552396898e-13</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001804137136787176</v>
+        <v>1.912599581748581e-13</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008514102082699537</v>
+        <v>3.624803636501778e-13</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001155912468675524</v>
+        <v>6.740838898351698e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006803765427321196</v>
+        <v>6.961470245744894e-13</v>
       </c>
       <c r="S3" t="n">
-        <v>0.000181289913598448</v>
+        <v>1.398095777604275e-13</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000521461945027113</v>
+        <v>1.4420990714515e-13</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004747249477077276</v>
+        <v>4.78951730706334e-13</v>
       </c>
       <c r="V3" t="n">
-        <v>3.358167305123061e-05</v>
+        <v>7.252626776053928e-13</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0007331662345677614</v>
+        <v>4.559648557160567e-13</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001071804144885391</v>
+        <v>4.993283889663525e-13</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.791470852680504e-05</v>
+        <v>2.700802634921645e-13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0002606003545224667</v>
+        <v>8.113505527151954e-13</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0003079265006817877</v>
+        <v>4.886429260352043e-13</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000258321117144078</v>
+        <v>7.772947866954705e-13</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.763523848960176e-05</v>
+        <v>5.309780393147889e-13</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0007456309394910932</v>
+        <v>3.436090930016011e-13</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0003125197254121304</v>
+        <v>2.063910294839572e-13</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0002298479957971722</v>
+        <v>9.883795713296062e-14</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0001066927798092365</v>
+        <v>3.994494893275885e-13</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.43904718849808e-05</v>
+        <v>4.214622899810505e-13</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0004506261320784688</v>
+        <v>8.14728818264443e-13</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0001223428407683969</v>
+        <v>4.24139862771275e-13</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0002209646627306938</v>
+        <v>1.908476089836075e-13</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0006450403016060591</v>
+        <v>2.619433261876608e-13</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0003735934151336551</v>
+        <v>4.402479899731637e-13</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.672999107744545e-05</v>
+        <v>2.606226324163019e-13</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0003484273620415479</v>
+        <v>1.361289146727465e-13</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0003725396818481386</v>
+        <v>8.010752434658985e-14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.568722993601114e-05</v>
+        <v>8.851452285973255e-14</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0001269438362214714</v>
+        <v>1.653171198025272e-12</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0003540088946465403</v>
+        <v>1.86822654107922e-14</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0008908382151275873</v>
+        <v>1.398103502544754e-13</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.002769257873296738</v>
+        <v>3.269824515317321e-12</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0004351093084551394</v>
+        <v>1.406186229740633e-13</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0001972818281501532</v>
+        <v>4.669901076080618e-13</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.001016476075164974</v>
+        <v>1.323456318494398e-12</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.001135148806497455</v>
+        <v>1.329723549152451e-12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0007406687363982201</v>
+        <v>1.005699429984519e-13</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0003283188561908901</v>
+        <v>4.64572065712876e-13</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0002488654863554984</v>
+        <v>1.962572899333326e-13</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.20054013072513e-05</v>
+        <v>5.653934351951273e-13</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.001182849169708788</v>
+        <v>1.698226628765731e-12</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.796719728503376e-06</v>
+        <v>2.201778391769729e-13</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.122574369423091e-05</v>
+        <v>1.32212513506702e-12</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.001964494818821549</v>
+        <v>9.878210445804503e-13</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0008147138287313282</v>
+        <v>8.22907551562696e-14</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0003127120435237885</v>
+        <v>7.973122487757445e-14</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0002668655361048877</v>
+        <v>5.416201883691463e-13</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0006750179454684258</v>
+        <v>1.798082190952732e-12</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0005787218688055873</v>
+        <v>1.455527186408276e-13</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0006579409819096327</v>
+        <v>4.473095342478334e-13</v>
       </c>
       <c r="BN3" t="n">
-        <v>8.480969700030982e-05</v>
+        <v>2.022624824788224e-13</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0003310281899757683</v>
+        <v>4.842175651328245e-14</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.000272013945505023</v>
+        <v>4.160640473642452e-13</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0002334980090381578</v>
+        <v>8.462752525660588e-13</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0001237021933775395</v>
+        <v>8.820166819134556e-13</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0002334989403607324</v>
+        <v>1.867512763355228e-13</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0001598736271262169</v>
+        <v>2.769458111191031e-13</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0004840019391849637</v>
+        <v>4.793023616889158e-13</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.001347736571915448</v>
+        <v>1.135504342462956e-12</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0001863660581875592</v>
+        <v>2.270074319493665e-13</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.000282908440567553</v>
+        <v>8.750331730901506e-13</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0002782925148494542</v>
+        <v>5.203670339678362e-14</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0002725061785895377</v>
+        <v>9.904535958754623e-13</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0002396176569163799</v>
+        <v>2.318911664252188e-13</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0001920713693834841</v>
+        <v>4.688452859454018e-13</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0003301118267700076</v>
+        <v>3.286421766776799e-14</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.000157724047312513</v>
+        <v>4.07880435156216e-13</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0007327881176024675</v>
+        <v>3.050584687202401e-13</v>
       </c>
       <c r="CF3" t="n">
-        <v>4.419838660396636e-06</v>
+        <v>2.548437196404733e-14</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.000310495583107695</v>
+        <v>1.488131449664531e-13</v>
       </c>
       <c r="CH3" t="n">
-        <v>8.545517630409449e-05</v>
+        <v>1.222952132357707e-13</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0002129405183950439</v>
+        <v>7.446038956856332e-14</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0004995304043404758</v>
+        <v>2.199441393986937e-13</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0001121359600801952</v>
+        <v>2.662768280609767e-13</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.000123724399600178</v>
+        <v>1.949266486070411e-13</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0009377010283060372</v>
+        <v>3.391846807761223e-13</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0004875122976955026</v>
+        <v>1.965228110453743e-12</v>
       </c>
       <c r="CO3" t="n">
-        <v>2.330585266463459e-05</v>
+        <v>6.684801366965698e-13</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.00165302655659616</v>
+        <v>1.023394151540569e-12</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0004862895584665239</v>
+        <v>1.844587579468565e-13</v>
       </c>
       <c r="CR3" t="n">
-        <v>5.232476178207435e-05</v>
+        <v>1.814978397608746e-12</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.001223181141540408</v>
+        <v>4.488469329284178e-13</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0008856923086568713</v>
+        <v>6.704639014115665e-13</v>
       </c>
       <c r="CU3" t="n">
-        <v>8.621608139947057e-05</v>
+        <v>3.736400295065168e-13</v>
       </c>
       <c r="CV3" t="n">
-        <v>9.101477917283773e-05</v>
+        <v>3.669457316127223e-13</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.0006992483977228403</v>
+        <v>1.972900602652608e-13</v>
       </c>
       <c r="CX3" t="n">
-        <v>4.099405487067997e-06</v>
+        <v>1.505498064538133e-14</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0004489694256335497</v>
+        <v>8.309695433920267e-14</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0001575700152898207</v>
+        <v>9.883065909708708e-14</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0002473506901878864</v>
+        <v>4.160141334067294e-14</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0004571193421725184</v>
+        <v>1.97463234457261e-14</v>
       </c>
       <c r="DC3" t="n">
-        <v>8.363937376998365e-05</v>
+        <v>1.893237763827063e-13</v>
       </c>
       <c r="DD3" t="n">
-        <v>6.393319927155972e-05</v>
+        <v>1.767376392805553e-13</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0004189565952401608</v>
+        <v>2.513210451381143e-13</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.000768067897297442</v>
+        <v>1.810466490267948e-12</v>
       </c>
       <c r="DG3" t="n">
-        <v>7.489915878977627e-05</v>
+        <v>1.261978369027084e-12</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.001128742704167962</v>
+        <v>4.262259490663001e-13</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.001548820175230503</v>
+        <v>1.063078878399404e-12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.000431833672337234</v>
+        <v>9.594662710816701e-14</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.0002729783882386982</v>
+        <v>3.594027202583061e-13</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0001431278651580215</v>
+        <v>7.267399030654043e-14</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0007193420897237957</v>
+        <v>6.366010149583268e-13</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.000198424982954748</v>
+        <v>1.07546641676861e-13</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.773059193510562e-05</v>
+        <v>1.823358358830213e-13</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.0006900549633428454</v>
+        <v>2.941167817106793e-13</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.0001729162904666737</v>
+        <v>1.053725357837154e-12</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0008904647547751665</v>
+        <v>5.854681973602172e-13</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.001113950274884701</v>
+        <v>1.281421664741864e-13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0003224838292226195</v>
+        <v>4.118985697226102e-13</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.0001511121372459456</v>
+        <v>7.646870875226142e-13</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.0001252857182407752</v>
+        <v>4.263605527660141e-13</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0001744265900924802</v>
+        <v>3.746248103397853e-13</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0003413674130570143</v>
+        <v>5.74257546896717e-13</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0002299275947734714</v>
+        <v>3.900432562109653e-14</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0006359651451930404</v>
+        <v>4.02384966709593e-13</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.000126040744362399</v>
+        <v>3.614210710226051e-13</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.0003735430655069649</v>
+        <v>3.976403624775249e-13</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0004688982153311372</v>
+        <v>1.043827350943882e-12</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0008573629893362522</v>
+        <v>4.055814657646234e-13</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.0006167390383780003</v>
+        <v>2.964653804567174e-13</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0002251849073218182</v>
+        <v>2.484974574203103e-13</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.000803942559286952</v>
+        <v>1.941390705964205e-14</v>
       </c>
       <c r="EH3" t="n">
-        <v>5.897191658732481e-05</v>
+        <v>1.954448701404349e-13</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0002464521676301956</v>
+        <v>1.342275493228587e-13</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0001346460194326937</v>
+        <v>2.635557787636356e-13</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0004521373193711042</v>
+        <v>1.697367832224905e-13</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.0004118478100281209</v>
+        <v>4.343535351270661e-13</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0002389772271271795</v>
+        <v>9.779717725748316e-14</v>
       </c>
       <c r="EN3" t="n">
-        <v>6.789116014260799e-05</v>
+        <v>3.130628080990489e-13</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.0002869319869205356</v>
+        <v>6.284732933722892e-13</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0005508110043592751</v>
+        <v>5.979659042226748e-13</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0002238417218904942</v>
+        <v>2.208168543849087e-13</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.0002440313255647197</v>
+        <v>3.855070559652396e-14</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.000251206016400829</v>
+        <v>1.893515184057948e-13</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0001054269669111818</v>
+        <v>1.903132192853166e-13</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.0004640755942091346</v>
+        <v>4.426893964251666e-13</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.0005453939666040242</v>
+        <v>7.030758353981925e-13</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.0004554288752842695</v>
+        <v>1.988354413843402e-13</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0002612034440971911</v>
+        <v>4.540417250075562e-13</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.000633681658655405</v>
+        <v>3.650089399568485e-13</v>
       </c>
       <c r="EZ3" t="n">
-        <v>8.35491155157797e-05</v>
+        <v>2.267521429953276e-14</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.0001367883232887834</v>
+        <v>1.340636044018517e-13</v>
       </c>
       <c r="FB3" t="n">
-        <v>9.831639908952639e-05</v>
+        <v>5.03673234304898e-14</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.0003912905231118202</v>
+        <v>1.836578849070958e-14</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.0004984073457308114</v>
+        <v>9.220829124117341e-14</v>
       </c>
       <c r="FE3" t="n">
-        <v>1.158328541350784e-05</v>
+        <v>1.742998513533031e-13</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.0001838742173276842</v>
+        <v>2.79424215970242e-13</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.0002067634777631611</v>
+        <v>1.718746672763061e-13</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.0002639983722474426</v>
+        <v>6.446389103943739e-13</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.0002564619644545019</v>
+        <v>2.519048066928348e-13</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.001234645955264568</v>
+        <v>6.444977472715163e-13</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.0003997833991888911</v>
+        <v>1.026400644164871e-13</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.0002270354598294944</v>
+        <v>3.927042610367415e-13</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.0003055518318433315</v>
+        <v>1.985681177861867e-13</v>
       </c>
       <c r="FN3" t="n">
-        <v>9.152745769824833e-05</v>
+        <v>1.935662865886964e-13</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.000128079394926317</v>
+        <v>3.850868463082385e-13</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.0008197508286684752</v>
+        <v>6.742640300261282e-13</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.000163751799846068</v>
+        <v>9.183665113099426e-13</v>
       </c>
       <c r="FR3" t="n">
-        <v>2.138915806426667e-05</v>
+        <v>7.376067530200092e-13</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.000701776472851634</v>
+        <v>5.719221212070746e-13</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.0001313896500505507</v>
+        <v>8.675011121776766e-13</v>
       </c>
       <c r="FU3" t="n">
-        <v>2.849863085430115e-05</v>
+        <v>9.896664515457107e-14</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.0004325404588598758</v>
+        <v>1.041386595013183e-12</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.0004767355567310005</v>
+        <v>1.74498436533721e-12</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.0001322892057942227</v>
+        <v>6.575945842544895e-13</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.000944619532674551</v>
+        <v>6.088795375010225e-13</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.0001065715114236809</v>
+        <v>7.031782925034924e-14</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.000122761630336754</v>
+        <v>6.6202956745115e-13</v>
       </c>
       <c r="GB3" t="n">
-        <v>1.649336263653822e-05</v>
+        <v>4.386385731632719e-13</v>
       </c>
       <c r="GC3" t="n">
-        <v>3.909628139808774e-05</v>
+        <v>1.578169154603862e-13</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.0004995089257135987</v>
+        <v>2.545674988082419e-13</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.000526284275110811</v>
+        <v>1.470378994342797e-13</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.0001916626060847193</v>
+        <v>9.933034212858405e-13</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.0003870390064548701</v>
+        <v>2.762837430624748e-13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3.230899991990555e-09</v>
+        <v>2.930894638097925e-09</v>
       </c>
       <c r="B4" t="n">
-        <v>1.976799701708387e-08</v>
+        <v>8.642888182919251e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9718703326308e-10</v>
+        <v>1.586023090638378e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.000717458372492e-08</v>
+        <v>3.641055457137554e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.079200977002984e-09</v>
+        <v>7.218011188747653e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.754690642259305e-10</v>
+        <v>5.841170658271722e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.095519674976231e-09</v>
+        <v>1.802140381368389e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>3.96832167126604e-09</v>
+        <v>3.755017186080067e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.334627018958258e-10</v>
+        <v>1.284785056121507e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>4.572096479193988e-09</v>
+        <v>6.15132278447561e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>1.391975157361003e-08</v>
+        <v>8.425180553217615e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>5.840491978936768e-10</v>
+        <v>2.416622901790788e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>1.105789859678907e-08</v>
+        <v>1.011791717075994e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.725595274621355e-09</v>
+        <v>6.721688095012723e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>8.976128285098639e-09</v>
+        <v>5.403296476913511e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>6.807999941571552e-09</v>
+        <v>5.932871971481291e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.487935604899576e-09</v>
+        <v>1.599776533467434e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.318211675018006e-10</v>
+        <v>1.548648875804304e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.696928649991719e-10</v>
+        <v>1.774408175947428e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>5.376254552658111e-09</v>
+        <v>1.228620094551047e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.517798220440625e-09</v>
+        <v>2.280434729939884e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>4.061387892662083e-10</v>
+        <v>1.377886138520523e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>6.339218039386196e-09</v>
+        <v>1.323456122470645e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>5.046522311147328e-09</v>
+        <v>1.682512906775457e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.278443904188634e-09</v>
+        <v>1.73309200324212e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.315159203763017e-09</v>
+        <v>1.660644954881718e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.937037362788942e-09</v>
+        <v>1.02782105049215e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.705835886577916e-10</v>
+        <v>4.869809000496161e-10</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.194250841418114e-12</v>
+        <v>2.669575227542964e-09</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.566192731061733e-09</v>
+        <v>6.017206732877867e-10</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.912254576907912e-09</v>
+        <v>1.530002013971909e-09</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.836255592024827e-09</v>
+        <v>2.198020238042275e-10</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.804155380646932e-09</v>
+        <v>5.59608448469362e-09</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.482786338158348e-09</v>
+        <v>1.737563537496101e-09</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.854789820678661e-09</v>
+        <v>7.274104873999931e-09</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.375495051192388e-09</v>
+        <v>3.423534511437509e-10</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.475403770851869e-10</v>
+        <v>1.855234854630794e-09</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.551353072201891e-09</v>
+        <v>1.091995271984558e-09</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.571430290920773e-10</v>
+        <v>3.890169963938206e-09</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.888537326522055e-09</v>
+        <v>1.188661835627158e-09</v>
       </c>
       <c r="AO4" t="n">
-        <v>9.384577559501395e-10</v>
+        <v>1.514246172895639e-09</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.277828953760718e-09</v>
+        <v>3.045751206798286e-09</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.49128362383999e-09</v>
+        <v>8.160959685810099e-10</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.205001153361309e-09</v>
+        <v>1.624438139558038e-09</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.553753430944994e-09</v>
+        <v>3.600261200276123e-10</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.906285073185245e-09</v>
+        <v>3.173184381921601e-09</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.237830282718733e-08</v>
+        <v>7.390600131884639e-09</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.111014391597109e-09</v>
+        <v>6.258570994788215e-09</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.0766547653418e-08</v>
+        <v>8.641120041730233e-10</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.504426609486245e-09</v>
+        <v>1.121804871218046e-08</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.849215721833502e-10</v>
+        <v>8.824637021120907e-09</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.71049785236255e-09</v>
+        <v>1.792223924823588e-09</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.43560468962778e-09</v>
+        <v>8.320492905777854e-11</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.510725932187597e-09</v>
+        <v>8.455031119680712e-10</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.324364256622857e-09</v>
+        <v>1.888489364887391e-09</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.557918487080315e-09</v>
+        <v>6.257541151910573e-10</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.314438584174241e-09</v>
+        <v>1.01943120611736e-10</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.34415389929643e-09</v>
+        <v>5.551142212567584e-09</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.082119531290118e-09</v>
+        <v>6.015016484894886e-09</v>
       </c>
       <c r="BH4" t="n">
-        <v>6.875396918459842e-10</v>
+        <v>3.215065991213351e-09</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.565589768937059e-09</v>
+        <v>1.873979416089355e-09</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.572007104135082e-09</v>
+        <v>4.270303222142502e-09</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.572583618880685e-09</v>
+        <v>6.465065149896532e-10</v>
       </c>
       <c r="BL4" t="n">
-        <v>2.782051478078529e-09</v>
+        <v>1.434339091943571e-09</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.918701642011911e-09</v>
+        <v>2.605001991895506e-09</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.863844799667504e-09</v>
+        <v>5.717053219722601e-11</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.889287837286702e-09</v>
+        <v>8.158860254070532e-10</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.387005066355584e-09</v>
+        <v>2.020208000885759e-09</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.91980670144676e-10</v>
+        <v>2.715294933341994e-10</v>
       </c>
       <c r="BR4" t="n">
-        <v>1.736949473141181e-09</v>
+        <v>1.076519318132796e-09</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.072620101742586e-11</v>
+        <v>2.498704798625795e-09</v>
       </c>
       <c r="BT4" t="n">
-        <v>3.862115488528772e-12</v>
+        <v>6.296157484264597e-10</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.459699359278147e-10</v>
+        <v>1.734766774674767e-09</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.806270296839557e-09</v>
+        <v>4.387541885364499e-09</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.398010818220996e-09</v>
+        <v>2.499896734065032e-09</v>
       </c>
       <c r="BX4" t="n">
-        <v>3.532916181825385e-09</v>
+        <v>5.941411251875195e-10</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.214970679619398e-09</v>
+        <v>3.084840827227708e-09</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.466331944754984e-09</v>
+        <v>3.883779964297673e-09</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.204493781439055e-09</v>
+        <v>2.654861441797607e-09</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.170556845371152e-09</v>
+        <v>7.789470735097836e-10</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.496243516920572e-09</v>
+        <v>3.951580174188507e-10</v>
       </c>
       <c r="CD4" t="n">
-        <v>7.767472776087914e-10</v>
+        <v>1.000116656157957e-09</v>
       </c>
       <c r="CE4" t="n">
-        <v>2.834923407135648e-09</v>
+        <v>3.634767153926077e-09</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.65873301152908e-09</v>
+        <v>1.227311030582712e-10</v>
       </c>
       <c r="CG4" t="n">
-        <v>1.308363639651589e-09</v>
+        <v>1.874501442955534e-09</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.357958079317712e-09</v>
+        <v>5.878343367626826e-10</v>
       </c>
       <c r="CI4" t="n">
-        <v>9.091536967709146e-10</v>
+        <v>1.070144195480793e-09</v>
       </c>
       <c r="CJ4" t="n">
-        <v>3.127020309356965e-10</v>
+        <v>7.29653004682973e-10</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.182577646918759e-10</v>
+        <v>7.267387247544832e-10</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.545706978551721e-09</v>
+        <v>5.612310061131609e-10</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.637086771173358e-09</v>
+        <v>3.153622918361521e-10</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.375902503042425e-09</v>
+        <v>5.048274243080186e-09</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.987801034886161e-10</v>
+        <v>6.205794100822004e-09</v>
       </c>
       <c r="CP4" t="n">
-        <v>3.222973443683941e-09</v>
+        <v>8.149247499034118e-09</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.460444654100002e-09</v>
+        <v>1.590865439382583e-09</v>
       </c>
       <c r="CR4" t="n">
-        <v>2.758091088850279e-09</v>
+        <v>9.52784184882205e-10</v>
       </c>
       <c r="CS4" t="n">
-        <v>5.840327776951426e-09</v>
+        <v>4.0988767935346e-10</v>
       </c>
       <c r="CT4" t="n">
-        <v>6.399374363752486e-09</v>
+        <v>2.704991342028507e-09</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.592885379153586e-09</v>
+        <v>1.607797228686536e-09</v>
       </c>
       <c r="CV4" t="n">
-        <v>9.325807903692862e-10</v>
+        <v>1.703326590885013e-09</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.277299238073738e-09</v>
+        <v>3.481228860735541e-09</v>
       </c>
       <c r="CX4" t="n">
-        <v>2.385459163534165e-09</v>
+        <v>7.30608351595663e-10</v>
       </c>
       <c r="CY4" t="n">
-        <v>3.493698441658921e-09</v>
+        <v>2.888191685812558e-09</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.229796597890243e-09</v>
+        <v>1.145642469779773e-09</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.355096812538648e-09</v>
+        <v>1.45237710746926e-09</v>
       </c>
       <c r="DB4" t="n">
-        <v>3.057210873347316e-10</v>
+        <v>8.42715730531296e-10</v>
       </c>
       <c r="DC4" t="n">
-        <v>6.018884279868075e-10</v>
+        <v>3.05074271400585e-10</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.656839554442513e-09</v>
+        <v>3.261332037762799e-10</v>
       </c>
       <c r="DE4" t="n">
-        <v>5.992116802744363e-10</v>
+        <v>1.300154428562905e-10</v>
       </c>
       <c r="DF4" t="n">
-        <v>6.065724034165498e-10</v>
+        <v>1.346974753957397e-09</v>
       </c>
       <c r="DG4" t="n">
-        <v>8.006822760364685e-09</v>
+        <v>1.422661988215168e-11</v>
       </c>
       <c r="DH4" t="n">
-        <v>1.775676317095076e-08</v>
+        <v>4.264094632944193e-10</v>
       </c>
       <c r="DI4" t="n">
-        <v>1.521711467944442e-08</v>
+        <v>3.940953674508307e-10</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.146223449488559e-09</v>
+        <v>5.533775659927187e-09</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.360601047968203e-09</v>
+        <v>2.852425629029653e-09</v>
       </c>
       <c r="DL4" t="n">
-        <v>1.130959947914789e-08</v>
+        <v>5.847286210780567e-09</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.32290178811445e-09</v>
+        <v>9.23934984076169e-10</v>
       </c>
       <c r="DN4" t="n">
-        <v>8.451398469944138e-10</v>
+        <v>1.484209199986708e-09</v>
       </c>
       <c r="DO4" t="n">
-        <v>8.479728030863498e-10</v>
+        <v>2.561456602379053e-10</v>
       </c>
       <c r="DP4" t="n">
-        <v>2.641214136289705e-09</v>
+        <v>1.120602055593167e-09</v>
       </c>
       <c r="DQ4" t="n">
-        <v>7.052051165246098e-10</v>
+        <v>5.924407631141548e-10</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.988926801033131e-09</v>
+        <v>1.673644334232449e-09</v>
       </c>
       <c r="DS4" t="n">
-        <v>2.586679759275512e-09</v>
+        <v>4.118196617053371e-10</v>
       </c>
       <c r="DT4" t="n">
-        <v>2.55016630035243e-09</v>
+        <v>6.678342323596098e-10</v>
       </c>
       <c r="DU4" t="n">
-        <v>6.245084449574279e-10</v>
+        <v>5.382408296839003e-09</v>
       </c>
       <c r="DV4" t="n">
-        <v>6.378251260485968e-09</v>
+        <v>2.059296067002947e-10</v>
       </c>
       <c r="DW4" t="n">
-        <v>1.061187138162722e-09</v>
+        <v>8.4481055484531e-10</v>
       </c>
       <c r="DX4" t="n">
-        <v>4.086353477816829e-09</v>
+        <v>2.611241223249294e-10</v>
       </c>
       <c r="DY4" t="n">
-        <v>4.866801628367057e-09</v>
+        <v>2.186831382644527e-09</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.958744277885671e-09</v>
+        <v>1.249859993279756e-09</v>
       </c>
       <c r="EA4" t="n">
-        <v>2.214332717187517e-09</v>
+        <v>1.16416276618736e-09</v>
       </c>
       <c r="EB4" t="n">
-        <v>5.237016598158561e-09</v>
+        <v>1.003797378551496e-09</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.540228722340942e-09</v>
+        <v>5.767891719798968e-10</v>
       </c>
       <c r="ED4" t="n">
-        <v>2.224959327890019e-09</v>
+        <v>4.901472117069261e-09</v>
       </c>
       <c r="EE4" t="n">
-        <v>4.218000948519318e-11</v>
+        <v>4.033160028171778e-09</v>
       </c>
       <c r="EF4" t="n">
-        <v>2.445581515075901e-10</v>
+        <v>2.029642232059814e-09</v>
       </c>
       <c r="EG4" t="n">
-        <v>1.913870728564859e-10</v>
+        <v>1.072453459372014e-09</v>
       </c>
       <c r="EH4" t="n">
-        <v>1.442453156919044e-09</v>
+        <v>2.035866586425072e-09</v>
       </c>
       <c r="EI4" t="n">
-        <v>1.651011993786256e-09</v>
+        <v>2.903689511057905e-09</v>
       </c>
       <c r="EJ4" t="n">
-        <v>2.332497306412051e-09</v>
+        <v>3.099853429500143e-10</v>
       </c>
       <c r="EK4" t="n">
-        <v>2.059243664476185e-09</v>
+        <v>7.20364656814354e-10</v>
       </c>
       <c r="EL4" t="n">
-        <v>5.950022141654188e-10</v>
+        <v>1.540128802268725e-09</v>
       </c>
       <c r="EM4" t="n">
-        <v>1.920299474988951e-09</v>
+        <v>4.122060193179067e-10</v>
       </c>
       <c r="EN4" t="n">
-        <v>1.294082729863533e-09</v>
+        <v>5.805169678296807e-10</v>
       </c>
       <c r="EO4" t="n">
-        <v>8.011852292710842e-10</v>
+        <v>3.942571824566699e-10</v>
       </c>
       <c r="EP4" t="n">
-        <v>3.378834989575807e-10</v>
+        <v>2.899473550144194e-09</v>
       </c>
       <c r="EQ4" t="n">
-        <v>3.243884716397361e-09</v>
+        <v>7.344802543940432e-11</v>
       </c>
       <c r="ER4" t="n">
-        <v>9.96331073199741e-11</v>
+        <v>4.063548941779516e-10</v>
       </c>
       <c r="ES4" t="n">
-        <v>4.096296635225372e-09</v>
+        <v>2.822470868135696e-10</v>
       </c>
       <c r="ET4" t="n">
-        <v>9.773163389681372e-10</v>
+        <v>1.085689427249292e-09</v>
       </c>
       <c r="EU4" t="n">
-        <v>8.834488141040708e-10</v>
+        <v>9.134142331390649e-10</v>
       </c>
       <c r="EV4" t="n">
-        <v>6.542349328952923e-09</v>
+        <v>1.299135243826299e-09</v>
       </c>
       <c r="EW4" t="n">
-        <v>1.161892915213514e-09</v>
+        <v>2.153895284351393e-09</v>
       </c>
       <c r="EX4" t="n">
-        <v>5.324863328048934e-10</v>
+        <v>9.474084849969699e-10</v>
       </c>
       <c r="EY4" t="n">
-        <v>2.388338860015438e-09</v>
+        <v>4.151062604762501e-09</v>
       </c>
       <c r="EZ4" t="n">
-        <v>2.45635045637016e-09</v>
+        <v>5.180738060772683e-10</v>
       </c>
       <c r="FA4" t="n">
-        <v>2.723467451559713e-09</v>
+        <v>3.141701121478491e-09</v>
       </c>
       <c r="FB4" t="n">
-        <v>7.32602367659041e-10</v>
+        <v>2.480786409631008e-10</v>
       </c>
       <c r="FC4" t="n">
-        <v>1.424007467498711e-09</v>
+        <v>7.240629762428341e-10</v>
       </c>
       <c r="FD4" t="n">
-        <v>7.438015758864935e-10</v>
+        <v>4.899634031829692e-10</v>
       </c>
       <c r="FE4" t="n">
-        <v>3.700697803754593e-10</v>
+        <v>6.690346054938345e-10</v>
       </c>
       <c r="FF4" t="n">
-        <v>2.357746886616496e-09</v>
+        <v>6.230498339476753e-10</v>
       </c>
       <c r="FG4" t="n">
-        <v>2.05570205302763e-09</v>
+        <v>3.347855048740911e-10</v>
       </c>
       <c r="FH4" t="n">
-        <v>2.435504298237134e-10</v>
+        <v>4.539779219214779e-09</v>
       </c>
       <c r="FI4" t="n">
-        <v>5.368395505911394e-09</v>
+        <v>2.512745567173624e-11</v>
       </c>
       <c r="FJ4" t="n">
-        <v>3.81137388316688e-09</v>
+        <v>2.953338684719142e-09</v>
       </c>
       <c r="FK4" t="n">
-        <v>1.744630884203957e-09</v>
+        <v>1.435725760501327e-09</v>
       </c>
       <c r="FL4" t="n">
-        <v>7.281989594654092e-11</v>
+        <v>7.961245551690865e-10</v>
       </c>
       <c r="FM4" t="n">
-        <v>2.311211444450123e-09</v>
+        <v>8.508053706002272e-10</v>
       </c>
       <c r="FN4" t="n">
-        <v>5.544189551898171e-09</v>
+        <v>2.627661643828105e-09</v>
       </c>
       <c r="FO4" t="n">
-        <v>4.273985609870579e-10</v>
+        <v>5.506600952998042e-09</v>
       </c>
       <c r="FP4" t="n">
-        <v>1.225818779815313e-09</v>
+        <v>2.194318476922419e-10</v>
       </c>
       <c r="FQ4" t="n">
-        <v>1.311197816988852e-09</v>
+        <v>7.46339967605536e-09</v>
       </c>
       <c r="FR4" t="n">
-        <v>9.235238684901503e-10</v>
+        <v>2.896036743749164e-09</v>
       </c>
       <c r="FS4" t="n">
-        <v>2.277111832427181e-10</v>
+        <v>9.259414346374228e-10</v>
       </c>
       <c r="FT4" t="n">
-        <v>1.280611350296113e-08</v>
+        <v>4.262304287294683e-09</v>
       </c>
       <c r="FU4" t="n">
-        <v>2.798384635127604e-09</v>
+        <v>4.762574778993667e-09</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.171982371734771e-09</v>
+        <v>2.172092727903419e-09</v>
       </c>
       <c r="FW4" t="n">
-        <v>8.78844164109438e-10</v>
+        <v>5.119543455833764e-09</v>
       </c>
       <c r="FX4" t="n">
-        <v>6.231695715008811e-10</v>
+        <v>9.480964902053302e-10</v>
       </c>
       <c r="FY4" t="n">
-        <v>3.4516152158659e-09</v>
+        <v>4.95911312015096e-10</v>
       </c>
       <c r="FZ4" t="n">
-        <v>1.437143737348379e-09</v>
+        <v>1.199265131646143e-09</v>
       </c>
       <c r="GA4" t="n">
-        <v>2.004838073332849e-09</v>
+        <v>4.452714641445255e-09</v>
       </c>
       <c r="GB4" t="n">
-        <v>2.081744998605473e-09</v>
+        <v>4.801836706036511e-10</v>
       </c>
       <c r="GC4" t="n">
-        <v>3.880254340060674e-09</v>
+        <v>4.246438756183579e-09</v>
       </c>
       <c r="GD4" t="n">
-        <v>4.327492586497783e-09</v>
+        <v>4.663949670913325e-09</v>
       </c>
       <c r="GE4" t="n">
-        <v>7.519693312474374e-09</v>
+        <v>1.010209471630219e-09</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.068062860376529e-09</v>
+        <v>2.173124180604447e-11</v>
       </c>
       <c r="GG4" t="n">
-        <v>2.843709712152531e-09</v>
+        <v>1.843367680720576e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0004255034145899117</v>
+        <v>8.068843726505293e-07</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003956995904445648</v>
+        <v>3.82082762371283e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003048740036319941</v>
+        <v>1.500590406067204e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001030808314681053</v>
+        <v>2.000504719035234e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002257700252812356</v>
+        <v>5.857611540704966e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002639460610225797</v>
+        <v>6.193402805365622e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002638289879541844</v>
+        <v>9.091723768506199e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001065477379597723</v>
+        <v>1.028460246743634e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003387940814718604</v>
+        <v>4.902158707409399e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000610139686614275</v>
+        <v>7.111930244718678e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003694251412525773</v>
+        <v>4.067338886670768e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>6.916800339240581e-05</v>
+        <v>2.027726441156119e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0009014616371132433</v>
+        <v>2.930601294792723e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003510309616103768</v>
+        <v>1.908121339511126e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002191398991271853</v>
+        <v>7.274984091054648e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>8.995467214845121e-05</v>
+        <v>8.405231710639782e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002992097288370132</v>
+        <v>1.604611952643609e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0004677131946664304</v>
+        <v>1.275744580198079e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>5.599947326118127e-05</v>
+        <v>1.091598642233294e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003037755377590656</v>
+        <v>2.636876956785272e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001016092501231469</v>
+        <v>3.645435526777874e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003423318266868591</v>
+        <v>1.652319406275637e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0005088745965622365</v>
+        <v>1.212501956615597e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0001192519630421884</v>
+        <v>1.369369965686928e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000162580021424219</v>
+        <v>4.85014243167825e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0005439206724986434</v>
+        <v>7.876063136791345e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002912664785981178</v>
+        <v>4.295229700801428e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.139442070387304e-05</v>
+        <v>1.276449984288774e-05</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.512801625533029e-05</v>
+        <v>2.196116838604212e-06</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0001028022234095261</v>
+        <v>1.240156871062936e-05</v>
       </c>
       <c r="AE5" t="n">
-        <v>5.413111284724437e-05</v>
+        <v>3.782886324188439e-06</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.124301141127944e-05</v>
+        <v>6.479753210442141e-06</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0001627655292395502</v>
+        <v>8.312790669151582e-06</v>
       </c>
       <c r="AH5" t="n">
-        <v>7.067713886499405e-05</v>
+        <v>3.224967713322258e-06</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.162087392003741e-05</v>
+        <v>2.600213156256359e-05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.020329364109784e-05</v>
+        <v>2.323565695405705e-06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0004984089755453169</v>
+        <v>1.10288765426958e-05</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0002539287379477173</v>
+        <v>4.133832135266857e-06</v>
       </c>
       <c r="AM5" t="n">
-        <v>6.688966823276132e-05</v>
+        <v>6.749011845386121e-06</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.000211075006518513</v>
+        <v>9.124670214077923e-06</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.825269181514159e-05</v>
+        <v>1.971346136997454e-06</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0005776796024292707</v>
+        <v>6.870028300909325e-06</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0001216299788211472</v>
+        <v>1.760620989443851e-06</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0002167235652450472</v>
+        <v>8.85525605553994e-06</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0003642851370386779</v>
+        <v>6.101910912548192e-06</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0001217123281094246</v>
+        <v>2.244655433969456e-06</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.002157969633117318</v>
+        <v>4.074860771652311e-05</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.000286352529656142</v>
+        <v>1.620658076717518e-05</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0002542654692661017</v>
+        <v>6.507908892672276e-06</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0001830537803471088</v>
+        <v>9.427834811503999e-06</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.001280622091144323</v>
+        <v>3.65711202903185e-05</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0006171708228066564</v>
+        <v>2.815390303112508e-07</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0003023049212060869</v>
+        <v>2.866241175070172e-06</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0005732027348130941</v>
+        <v>1.602632664798875e-06</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0002454704372212291</v>
+        <v>7.148008080548607e-06</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0009195111342705786</v>
+        <v>5.390165370044997e-06</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0008074177312664688</v>
+        <v>7.62492663852754e-06</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0001004175865091383</v>
+        <v>2.424925924060517e-06</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0002287433599121869</v>
+        <v>2.027258051384706e-05</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0005853424081578851</v>
+        <v>1.725781658024061e-06</v>
       </c>
       <c r="BI5" t="n">
-        <v>9.594751463737339e-05</v>
+        <v>1.009875086310785e-05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0002440657408442348</v>
+        <v>1.224246443598531e-05</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0004448427353054285</v>
+        <v>9.169516488327645e-07</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0001704685273580253</v>
+        <v>3.908519829565194e-06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0007065776153467596</v>
+        <v>1.816310759750195e-05</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.000359419354936108</v>
+        <v>1.366572746519523e-06</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.759163205861114e-05</v>
+        <v>9.362944183521904e-06</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0003918875299859792</v>
+        <v>1.1078225725214e-05</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.975456249667332e-05</v>
+        <v>7.322641522478079e-06</v>
       </c>
       <c r="BR5" t="n">
-        <v>3.081990871578455e-05</v>
+        <v>5.321273874869803e-06</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0001891666470328346</v>
+        <v>5.263352250040043e-06</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.617577259428799e-05</v>
+        <v>6.854496859887149e-06</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.534712545340881e-05</v>
+        <v>6.530365681101102e-06</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001418634317815304</v>
+        <v>1.806990621844307e-05</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0002391386515228078</v>
+        <v>3.807610482908785e-06</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0002036344085354358</v>
+        <v>1.00325487437658e-05</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.22620965866372e-05</v>
+        <v>6.563960596395191e-06</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0004408966342452914</v>
+        <v>2.896263140428346e-05</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.33794183563441e-05</v>
+        <v>1.024493394652382e-05</v>
       </c>
       <c r="CB5" t="n">
-        <v>8.751489804126322e-05</v>
+        <v>3.212738192814868e-06</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0002612083917483687</v>
+        <v>2.038854745478602e-06</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.361324242083356e-05</v>
+        <v>2.03532408704632e-06</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0006860506255179644</v>
+        <v>1.188968053611461e-05</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0002680476172827184</v>
+        <v>3.166306214552606e-06</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.223546658176929e-05</v>
+        <v>3.581567625587923e-06</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0001748300710460171</v>
+        <v>2.965566636703443e-07</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0003570942499209195</v>
+        <v>1.480129049014067e-05</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0002173720276914537</v>
+        <v>1.03528202544112e-06</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0001972071186173707</v>
+        <v>2.364054580539232e-06</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0002467306912876666</v>
+        <v>1.264424099645112e-06</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0008261304465122521</v>
+        <v>6.046218004485127e-06</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0003797603712882847</v>
+        <v>9.915291229845025e-06</v>
       </c>
       <c r="CO5" t="n">
-        <v>2.078979377984069e-05</v>
+        <v>1.382376103720162e-05</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.000776873785071075</v>
+        <v>9.215639238391304e-07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0003282352117821574</v>
+        <v>1.030331441143062e-05</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0008610184886492789</v>
+        <v>3.494541033433052e-06</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0006452709203585982</v>
+        <v>1.376512227579951e-05</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0005626322235912085</v>
+        <v>1.545864506624639e-05</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.000188414822332561</v>
+        <v>4.654866643249989e-06</v>
       </c>
       <c r="CV5" t="n">
-        <v>5.812769086332992e-05</v>
+        <v>2.311725211256999e-06</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0006791040650568902</v>
+        <v>1.141987104347209e-05</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.000289508025161922</v>
+        <v>5.240487553237472e-06</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0002724624937400222</v>
+        <v>6.342663255054504e-06</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0001499124045949429</v>
+        <v>8.744914339331444e-07</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0003764056018553674</v>
+        <v>1.642673305468634e-05</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0001967511198017746</v>
+        <v>1.357677774649346e-07</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0004031293792650104</v>
+        <v>3.046729034394957e-06</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0001854273141361773</v>
+        <v>2.224257286798093e-06</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0002413143665762618</v>
+        <v>3.69694294022338e-06</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0008328052936121821</v>
+        <v>2.705760743992869e-05</v>
       </c>
       <c r="DG5" t="n">
-        <v>9.869814675766975e-05</v>
+        <v>1.093111677619163e-05</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0006684957770630717</v>
+        <v>6.055734047549777e-07</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0009238337515853345</v>
+        <v>2.539811703172745e-06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0005755508900620043</v>
+        <v>5.869437245564768e-06</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0001632122730370611</v>
+        <v>6.750467491656309e-07</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0005784230306744576</v>
+        <v>2.012251752603333e-05</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0006909281946718693</v>
+        <v>1.083892493625171e-05</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0001956389751285315</v>
+        <v>7.495299541915301e-06</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0003800608101300895</v>
+        <v>1.303931276197545e-05</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0002604296314530075</v>
+        <v>3.39620009981445e-06</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0002583188761491328</v>
+        <v>9.131055776379071e-06</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0002787348930723965</v>
+        <v>5.918876922805794e-06</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0003299675590824336</v>
+        <v>1.68966125784209e-05</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0003177872858941555</v>
+        <v>4.367788733361522e-06</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0001969027216546237</v>
+        <v>1.658963628869969e-05</v>
       </c>
       <c r="DV5" t="n">
-        <v>3.045959601877257e-05</v>
+        <v>1.980327851924812e-06</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.904921373352408e-05</v>
+        <v>2.244140887341928e-06</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0004809369274880737</v>
+        <v>9.101671594180516e-07</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0001837037998484448</v>
+        <v>2.056725134025328e-05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0002387367130722851</v>
+        <v>3.897276201314526e-06</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0003314139321446419</v>
+        <v>8.502935088472441e-06</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0003163805231451988</v>
+        <v>4.61512581750867e-06</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0001287844643229619</v>
+        <v>4.849627202929696e-06</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.000144647405249998</v>
+        <v>5.923368462390499e-06</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0006098562735132873</v>
+        <v>1.587775113875978e-05</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0003790656919591129</v>
+        <v>7.71501504459593e-07</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0006477800197899342</v>
+        <v>1.574174234519887e-06</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0003893557877745479</v>
+        <v>1.04905439002323e-06</v>
       </c>
       <c r="EI5" t="n">
-        <v>3.397038381081074e-05</v>
+        <v>1.229415374837117e-06</v>
       </c>
       <c r="EJ5" t="n">
-        <v>7.558269135188311e-05</v>
+        <v>4.223143150738906e-06</v>
       </c>
       <c r="EK5" t="n">
-        <v>3.369434125488624e-05</v>
+        <v>6.151482921268325e-06</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0002129989734385163</v>
+        <v>1.535053115730989e-07</v>
       </c>
       <c r="EM5" t="n">
-        <v>3.729626041604206e-05</v>
+        <v>3.502400431898423e-07</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0001187174275401048</v>
+        <v>7.429562629113207e-06</v>
       </c>
       <c r="EO5" t="n">
-        <v>3.49514521076344e-05</v>
+        <v>3.100532012467738e-06</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0004469201085157692</v>
+        <v>8.179385986295529e-06</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0001036429312080145</v>
+        <v>5.605744263448287e-06</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0002495280059520155</v>
+        <v>1.586096550454386e-05</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.000374882947653532</v>
+        <v>1.187651469081175e-05</v>
       </c>
       <c r="ET5" t="n">
-        <v>9.043962563737296e-06</v>
+        <v>2.310815716555226e-06</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0006495352135971189</v>
+        <v>7.974317668413278e-07</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0008726640371605754</v>
+        <v>4.478612027014606e-06</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0001019265182549134</v>
+        <v>6.152488822408486e-06</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0001201997147290967</v>
+        <v>1.305295882048085e-06</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0006397560937330127</v>
+        <v>1.29825984913623e-05</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0002030371833825484</v>
+        <v>3.285827233412419e-06</v>
       </c>
       <c r="FA5" t="n">
-        <v>7.646518497494981e-05</v>
+        <v>6.754899914085399e-06</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0001279828284168616</v>
+        <v>1.517557166152983e-06</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0003175156889483333</v>
+        <v>1.628690733923577e-05</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0003280354430899024</v>
+        <v>4.089683443453396e-06</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0002953493385575712</v>
+        <v>3.40009069077496e-06</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0002810860460158437</v>
+        <v>4.856470241065836e-06</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.00021553342230618</v>
+        <v>4.612434167938773e-08</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0002270610712002963</v>
+        <v>7.787500180711504e-06</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0001693802332738414</v>
+        <v>1.237620745087042e-05</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0005051980842836201</v>
+        <v>6.788678092561895e-06</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0002422384568490088</v>
+        <v>1.225943378813099e-06</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.000267449242528528</v>
+        <v>1.418260944774374e-05</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0001743423199513927</v>
+        <v>2.09132213058183e-06</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0002096672542393208</v>
+        <v>1.758939833962359e-05</v>
       </c>
       <c r="FO5" t="n">
-        <v>8.843983232509345e-05</v>
+        <v>1.268153937417082e-05</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.000381608319003135</v>
+        <v>1.045213502948172e-05</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0003122666385024786</v>
+        <v>1.041085943143116e-05</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0005467231385409832</v>
+        <v>1.697126208455302e-06</v>
       </c>
       <c r="FS5" t="n">
-        <v>8.521737618139014e-05</v>
+        <v>1.484397671447368e-05</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0002122037985827774</v>
+        <v>2.767435034911614e-06</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0004052307922393084</v>
+        <v>1.553817128296942e-05</v>
       </c>
       <c r="FV5" t="n">
-        <v>7.092993473634124e-05</v>
+        <v>6.127853794168914e-06</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0001393567072227597</v>
+        <v>3.045400080736727e-05</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0002517795073799789</v>
+        <v>6.20098353465437e-06</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0004782378673553467</v>
+        <v>4.224064014124451e-06</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0002620237064547837</v>
+        <v>3.7026343306934e-06</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0002982175501529127</v>
+        <v>1.512464768893551e-05</v>
       </c>
       <c r="GB5" t="n">
-        <v>2.113602204190101e-05</v>
+        <v>3.320282985441736e-06</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0003242890525143594</v>
+        <v>1.702062581898645e-05</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0003409685159567744</v>
+        <v>1.218788293044781e-05</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0005692249396815896</v>
+        <v>4.663859272113768e-06</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0001957312051672488</v>
+        <v>7.059079507598653e-06</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0002182447497034445</v>
+        <v>1.620402485968953e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0005454214988276362</v>
+        <v>1.289055973074937e-09</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01625523716211319</v>
+        <v>6.084276638063102e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001497190678492188</v>
+        <v>3.572778739524551e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00452286284416914</v>
+        <v>5.980814732353679e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005872377194464207</v>
+        <v>3.724871522337025e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0122437784448266</v>
+        <v>1.654557824082303e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007506826659664512</v>
+        <v>7.818643510404399e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002912845462560654</v>
+        <v>3.089951405854663e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002156180853489786</v>
+        <v>1.394337645344024e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001857530092820525</v>
+        <v>2.539231047649082e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01610695756971836</v>
+        <v>2.832422740794982e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005648268852382898</v>
+        <v>3.092703870777314e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003366400022059679</v>
+        <v>1.631076163022271e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003046143567189574</v>
+        <v>2.518184993860473e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01128971483558416</v>
+        <v>5.265377023278006e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>8.992105722427368e-05</v>
+        <v>6.88263543380252e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001524762599729002</v>
+        <v>7.236452326253584e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003247752902098</v>
+        <v>4.248772444981341e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001463050430174917</v>
+        <v>7.617134478721255e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001476283185184002</v>
+        <v>4.321977442600655e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00119210802949965</v>
+        <v>4.974862299889082e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002266617957502604</v>
+        <v>1.035207475297284e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001922630239278078</v>
+        <v>4.331789149603082e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0008939866675063968</v>
+        <v>2.400013077163976e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001359955058433115</v>
+        <v>6.253175199866234e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001671331934630871</v>
+        <v>4.060791702897859e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001126968418247998</v>
+        <v>3.674903714667721e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001287391409277916</v>
+        <v>7.536745449954196e-09</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0004684462037403136</v>
+        <v>1.089704104728639e-09</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.001083794282749295</v>
+        <v>6.942166397294613e-09</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.001298482995480299</v>
+        <v>3.125637748624399e-09</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.000699612544849515</v>
+        <v>6.504635718940222e-10</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001410837867297232</v>
+        <v>1.915664293861141e-09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0003631742438301444</v>
+        <v>3.504432743994812e-09</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0001966596173588187</v>
+        <v>1.359959922453413e-09</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0006383884465321898</v>
+        <v>3.338765486304851e-09</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.001705486560240388</v>
+        <v>5.139828118672085e-09</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.002040565479546785</v>
+        <v>2.676589616612546e-09</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.002089374931529164</v>
+        <v>2.306868918111604e-09</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0004802254843525589</v>
+        <v>7.060722562179933e-10</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0004670786729548126</v>
+        <v>8.42904501752173e-09</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.001454204088076949</v>
+        <v>1.499426471873733e-09</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0003857046249322593</v>
+        <v>3.470854048615024e-09</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0009088849765248597</v>
+        <v>1.115935521767142e-08</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0007168176816776395</v>
+        <v>7.405152602224518e-10</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0008006051066331565</v>
+        <v>4.03481337230005e-09</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.0108489990234375</v>
+        <v>9.268581457888558e-09</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.002439755015075207</v>
+        <v>4.603174286188505e-09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.001989240990951657</v>
+        <v>1.763663215470501e-09</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.002733486006036401</v>
+        <v>9.133244383008332e-09</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.005671667400747538</v>
+        <v>3.814387028455712e-09</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.001198637299239635</v>
+        <v>2.428751644245608e-09</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0005762355285696685</v>
+        <v>2.01080196937653e-09</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.001221068669110537</v>
+        <v>6.699976684565456e-10</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.001248588319867849</v>
+        <v>1.324987586315274e-08</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.003438485786318779</v>
+        <v>7.952413838552275e-09</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.003816984826698899</v>
+        <v>7.08592851061951e-10</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.158021278679371e-05</v>
+        <v>3.344293508789065e-09</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.004620763938874006</v>
+        <v>1.390017967395352e-08</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0058977035805583</v>
+        <v>1.342134736681544e-09</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0009158914326690137</v>
+        <v>5.008730652455995e-10</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2.464649151079357e-05</v>
+        <v>3.707909534966802e-09</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0004653356445487589</v>
+        <v>6.893063897450702e-09</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.001734983641654253</v>
+        <v>2.376668861714393e-09</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.00352020887658</v>
+        <v>3.736310816293553e-09</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0004903689259663224</v>
+        <v>2.343647276248362e-09</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0002246757067041472</v>
+        <v>1.203545596517586e-09</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.002036673715338111</v>
+        <v>4.89430806993596e-09</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.00128580117598176</v>
+        <v>2.225006845435473e-09</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.001003482146188617</v>
+        <v>3.084871469383188e-09</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0006978707388043404</v>
+        <v>6.533815155584932e-10</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0008483120473101735</v>
+        <v>5.233156130657335e-09</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0003634249733295292</v>
+        <v>7.366332432923173e-09</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.006389915477484465</v>
+        <v>9.612686646676138e-09</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0002323786029592156</v>
+        <v>3.631084322108791e-09</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.002145980950444937</v>
+        <v>4.215999105383617e-09</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0007235720404423773</v>
+        <v>2.665764053944031e-09</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.00117104675155133</v>
+        <v>3.160690820180889e-09</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0005629559746012092</v>
+        <v>5.163136140851066e-09</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0003889481304213405</v>
+        <v>2.992001091328689e-11</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0008172967936843634</v>
+        <v>1.261103554917042e-09</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.24628620344447e-05</v>
+        <v>7.437176430258319e-10</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.002531934063881636</v>
+        <v>4.577234702374255e-10</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0005130780627951026</v>
+        <v>1.631621948661177e-09</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0007460180204361677</v>
+        <v>5.803523217551287e-10</v>
       </c>
       <c r="CH6" t="n">
-        <v>4.650610935641453e-05</v>
+        <v>1.654781200954858e-09</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.002322885673493147</v>
+        <v>7.9083850579309e-10</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.00112171215005219</v>
+        <v>1.39503808505026e-09</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0001221298734890297</v>
+        <v>1.870902321954304e-09</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0003881070879288018</v>
+        <v>3.732366860020875e-09</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.004200194496661425</v>
+        <v>2.097666262912412e-09</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.001052217907272279</v>
+        <v>1.088451728747941e-08</v>
       </c>
       <c r="CO6" t="n">
-        <v>5.78495382796973e-05</v>
+        <v>2.704766410843717e-09</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.00141188339330256</v>
+        <v>3.753017896457322e-09</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0001848154934123158</v>
+        <v>6.13487038947369e-09</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0004256323736626655</v>
+        <v>4.307986856133539e-09</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.00254309456795454</v>
+        <v>1.112494452115698e-08</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.003577510826289654</v>
+        <v>6.36364294592795e-10</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0009522503241896629</v>
+        <v>5.137247072184437e-09</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.022521948674694e-05</v>
+        <v>5.252581147807689e-10</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.00215311418287456</v>
+        <v>1.155032736122052e-09</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0003672969760373235</v>
+        <v>2.756581407581393e-09</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.001357351429760456</v>
+        <v>1.421208706275934e-10</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0002125874743796885</v>
+        <v>1.881397926339901e-09</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.002277829218655825</v>
+        <v>4.863893732220959e-10</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0009997353190556169</v>
+        <v>7.675618474145551e-10</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.0006635920726694167</v>
+        <v>8.753724967114351e-10</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0003222009108867496</v>
+        <v>3.173910911868916e-09</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.001272238907404244</v>
+        <v>9.061371653018568e-10</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.003954384010285139</v>
+        <v>9.992934479896576e-09</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0004079407081007957</v>
+        <v>1.030114926692249e-08</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.002324606757611036</v>
+        <v>3.659065939132233e-09</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.003427905263379216</v>
+        <v>7.342926711118025e-09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.001435493002645671</v>
+        <v>1.102198776692376e-09</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.001005460857413709</v>
+        <v>3.196588771459119e-09</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0005385723197832704</v>
+        <v>2.957245337498193e-09</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.003274807939305902</v>
+        <v>3.365703271640541e-09</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0006686208653263748</v>
+        <v>3.305347995308239e-09</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0003184242523275316</v>
+        <v>1.723019948940419e-09</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.001412170939147472</v>
+        <v>1.800000148932668e-09</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.001190336188301444</v>
+        <v>3.785605717787632e-10</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0007994695333763957</v>
+        <v>2.306406843288755e-09</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.001439801184460521</v>
+        <v>2.963229439600923e-09</v>
       </c>
       <c r="DT6" t="n">
-        <v>3.0666240490973e-05</v>
+        <v>7.35766336745769e-10</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.000350749702192843</v>
+        <v>1.564729679159882e-09</v>
       </c>
       <c r="DV6" t="n">
-        <v>5.680660251528025e-05</v>
+        <v>4.800715380781639e-09</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.001248554908670485</v>
+        <v>3.912059565180925e-10</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.002243436174467206</v>
+        <v>3.618644717207076e-09</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0002981010475195944</v>
+        <v>5.476629816314471e-09</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0005234592244960368</v>
+        <v>1.597235010919462e-09</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.002001365646719933</v>
+        <v>1.342994049302604e-09</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.001498113269917667</v>
+        <v>2.521386877063492e-09</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0005607236525975168</v>
+        <v>1.335624411069603e-08</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0009455551626160741</v>
+        <v>2.021768086279963e-09</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0002478538081049919</v>
+        <v>2.57146171023237e-09</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.000266030547209084</v>
+        <v>8.885733260299844e-10</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.002624849788844585</v>
+        <v>3.995997754913105e-09</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0005689936806447804</v>
+        <v>1.837328622578127e-10</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0009999028407037258</v>
+        <v>2.296940859736196e-09</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.000285821792203933</v>
+        <v>3.044414498276637e-09</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.002272015204653144</v>
+        <v>2.272412813475455e-10</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.001357325469143689</v>
+        <v>4.974288980719166e-09</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0007437686435878277</v>
+        <v>5.903754152214447e-10</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.000417462142650038</v>
+        <v>8.657074168638701e-09</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.000110877153929323</v>
+        <v>1.412588934712744e-09</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.00166855868883431</v>
+        <v>2.955288236350384e-09</v>
       </c>
       <c r="EQ6" t="n">
-        <v>4.113116301596165e-05</v>
+        <v>8.87374951297204e-10</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0002278291503898799</v>
+        <v>2.463912407435487e-09</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0008853145991452038</v>
+        <v>1.283322559331168e-09</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.001663882518187165</v>
+        <v>5.668157943006236e-09</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.001278329757042229</v>
+        <v>4.374454576350217e-09</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.002271594945341349</v>
+        <v>1.394041770907961e-09</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.001200957107357681</v>
+        <v>6.503160232540495e-10</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0002996961411554366</v>
+        <v>2.518402431039846e-10</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.001987656345590949</v>
+        <v>1.548848826971039e-10</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0001587776932865381</v>
+        <v>1.432377549903663e-09</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0008022054680623114</v>
+        <v>1.211750699781078e-10</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0005340114003047347</v>
+        <v>2.627872586202784e-09</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.00233933818526566</v>
+        <v>1.763260926157528e-10</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.001103174756281078</v>
+        <v>2.148816402591791e-10</v>
       </c>
       <c r="FE6" t="n">
-        <v>1.028009501169436e-05</v>
+        <v>3.067133491629903e-10</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.0002882552798837423</v>
+        <v>3.320051567001769e-09</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0003350505139678717</v>
+        <v>2.33005770233774e-09</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.001560766017064452</v>
+        <v>6.205692848482158e-09</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0004754961701110005</v>
+        <v>1.402775007264268e-09</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.00275619700551033</v>
+        <v>3.303086693051682e-09</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0006520437309518456</v>
+        <v>1.081057576790556e-09</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0007192856865003705</v>
+        <v>4.367461503562708e-09</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0003499537997413427</v>
+        <v>6.824880660616373e-09</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0008158191340044141</v>
+        <v>1.915961389542531e-09</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.000901720835827291</v>
+        <v>7.973257609705797e-09</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.001595896203070879</v>
+        <v>8.963871422906777e-09</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.003176171565428376</v>
+        <v>5.23071141955711e-09</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0008429232402704656</v>
+        <v>6.250966411158743e-09</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.002111445181071758</v>
+        <v>8.041651788914805e-09</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.002307629678398371</v>
+        <v>1.119444981156903e-08</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0001178093807538971</v>
+        <v>1.222961509839138e-09</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.001097344676963985</v>
+        <v>8.431882747572672e-09</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.002071138471364975</v>
+        <v>1.609465805074706e-08</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.001154277939349413</v>
+        <v>1.590458098554848e-09</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.002219459740445018</v>
+        <v>3.710052265404329e-10</v>
       </c>
       <c r="FZ6" t="n">
-        <v>4.247541073709726e-05</v>
+        <v>2.532293486012804e-09</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.000117068862891756</v>
+        <v>7.070120933150292e-09</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0001461224746890366</v>
+        <v>1.256718284992075e-09</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.001124155474826694</v>
+        <v>4.543188047989588e-10</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0001779448648449033</v>
+        <v>2.58500387761984e-10</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.002558910986408591</v>
+        <v>2.765454976128012e-09</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0009751877514645457</v>
+        <v>5.62647217705603e-09</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0001598875969648361</v>
+        <v>1.413205108491411e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4.697417807619786e-06</v>
+        <v>2.793689418467693e-06</v>
       </c>
       <c r="B7" t="n">
-        <v>7.159011147450656e-05</v>
+        <v>4.410640394780785e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>5.728486939915456e-06</v>
+        <v>2.486726407369133e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.458552262396552e-05</v>
+        <v>3.021169322892092e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.260513363376958e-05</v>
+        <v>4.917795649816981e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.110053381125908e-05</v>
+        <v>5.017433068132959e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.906276666995836e-06</v>
+        <v>9.169219993054867e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.407050816254923e-06</v>
+        <v>1.73596381500829e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>4.017840637970949e-06</v>
+        <v>2.527904996441066e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.163503293355461e-05</v>
+        <v>2.002706196435611e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>5.673584018950351e-05</v>
+        <v>4.439210169948637e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.874947201940813e-06</v>
+        <v>3.059143273276277e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.453771958244033e-05</v>
+        <v>4.893088043900207e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.901357609312981e-05</v>
+        <v>2.648861118359491e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.351997500227299e-05</v>
+        <v>4.719779826700687e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>9.627012332202867e-06</v>
+        <v>1.044368764269166e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.080939677602146e-06</v>
+        <v>6.886249138915446e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>6.998352546361275e-07</v>
+        <v>3.539872295732494e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.763050699490122e-06</v>
+        <v>4.785458258993458e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>9.738206244946923e-06</v>
+        <v>3.228564310120419e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>3.955487045459449e-06</v>
+        <v>6.99822157912422e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>4.07214656661381e-06</v>
+        <v>6.347266662487527e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.152877525280928e-06</v>
+        <v>1.029817849484971e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>9.53620474319905e-06</v>
+        <v>9.458307431486901e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.520108177530346e-06</v>
+        <v>2.300808773725294e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.244585018866928e-05</v>
+        <v>5.25306495546829e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.036858500621747e-06</v>
+        <v>1.684411188307422e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.080948540125974e-06</v>
+        <v>1.911599269988074e-07</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.239779511612142e-06</v>
+        <v>4.86944099975517e-06</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.516268851759378e-07</v>
+        <v>8.624278052593581e-06</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.540609784773551e-07</v>
+        <v>4.617845661414322e-06</v>
       </c>
       <c r="AF7" t="n">
-        <v>4.532029720394348e-07</v>
+        <v>3.68507471648627e-06</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.121713239626843e-06</v>
+        <v>2.430454514978919e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.3216082303843e-06</v>
+        <v>1.913505911943503e-06</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.934572310346994e-06</v>
+        <v>2.453114575473592e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.071658855129499e-06</v>
+        <v>3.273118636570871e-06</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.404315743362531e-06</v>
+        <v>5.337045422493247e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>7.890887900430243e-06</v>
+        <v>1.248356784344651e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.847802991505887e-06</v>
+        <v>7.390577593469061e-06</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.372177161509171e-06</v>
+        <v>7.543640094809234e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>6.910226147738285e-06</v>
+        <v>2.253638513138867e-06</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.17995682558103e-06</v>
+        <v>5.394592790253228e-06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.049917727868888e-06</v>
+        <v>8.741031933823251e-07</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.223623240155575e-07</v>
+        <v>1.19217902465607e-05</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.42370116818347e-06</v>
+        <v>2.620160785227199e-06</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.752872311859392e-06</v>
+        <v>3.759380206247442e-06</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.411457848618738e-05</v>
+        <v>3.754218050744385e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.878106781485258e-06</v>
+        <v>1.643792711547576e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.27389737626072e-06</v>
+        <v>1.672279358899686e-05</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.292004971124697e-06</v>
+        <v>3.001317054440733e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.785055575164733e-06</v>
+        <v>2.320704516023397e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.77086996397702e-06</v>
+        <v>1.026042582452646e-06</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.958700957213296e-07</v>
+        <v>8.204595360439271e-06</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.156961388915079e-05</v>
+        <v>5.872375822946196e-06</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.450024339850643e-06</v>
+        <v>4.390659341879655e-06</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.722868000797462e-05</v>
+        <v>8.482054909109138e-06</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.683407390373759e-05</v>
+        <v>1.589296880410984e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.713658207336266e-06</v>
+        <v>5.778984814241994e-06</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.100140889320755e-05</v>
+        <v>1.765670276654419e-05</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.882884928112617e-06</v>
+        <v>1.41646851261612e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>9.58591317612445e-06</v>
+        <v>1.192371200886555e-06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>5.282739493850386e-06</v>
+        <v>4.527076725935331e-06</v>
       </c>
       <c r="BK7" t="n">
-        <v>2.439102217977052e-07</v>
+        <v>3.90016907658719e-07</v>
       </c>
       <c r="BL7" t="n">
-        <v>3.290353333795792e-06</v>
+        <v>3.973309503635392e-07</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.071472282405011e-06</v>
+        <v>1.359734596917406e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.100390090869041e-05</v>
+        <v>5.830814643559279e-06</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.34332867168996e-06</v>
+        <v>2.395679075561929e-06</v>
       </c>
       <c r="BP7" t="n">
-        <v>6.49581988909631e-06</v>
+        <v>2.846665438482887e-06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.572186516175861e-07</v>
+        <v>9.088306796911638e-06</v>
       </c>
       <c r="BR7" t="n">
-        <v>2.843796437446144e-06</v>
+        <v>1.112061454477953e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.958050916073262e-06</v>
+        <v>1.058302132150857e-06</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.575059847411467e-06</v>
+        <v>3.686299805849558e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.33730122797715e-06</v>
+        <v>7.374168944807025e-06</v>
       </c>
       <c r="BV7" t="n">
-        <v>2.50920893449802e-05</v>
+        <v>2.612518619571347e-05</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.111915354267694e-06</v>
+        <v>1.275843897019513e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>7.035103408270516e-06</v>
+        <v>2.216939537902363e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.249843307959964e-06</v>
+        <v>9.616866009309888e-06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.416195229670848e-06</v>
+        <v>1.6647865777486e-05</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.361317794770002e-06</v>
+        <v>7.764162546664011e-06</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.574744939920492e-06</v>
+        <v>1.04782839116524e-06</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.141544756450457e-06</v>
+        <v>2.464533281454351e-06</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.804520242236322e-08</v>
+        <v>4.18572744820267e-06</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.17317258627736e-05</v>
+        <v>1.423116373189259e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>6.668075911875349e-06</v>
+        <v>5.174750640435377e-06</v>
       </c>
       <c r="CG7" t="n">
-        <v>1.210603159051971e-06</v>
+        <v>8.557617547921836e-06</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.599906227056636e-06</v>
+        <v>1.647076715016738e-06</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.788244162526098e-06</v>
+        <v>1.076035277947085e-05</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.498928779459675e-06</v>
+        <v>2.340209448448149e-06</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.123883635045786e-06</v>
+        <v>4.732161414722214e-06</v>
       </c>
       <c r="CL7" t="n">
-        <v>3.96954828829621e-06</v>
+        <v>3.801981392825837e-06</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.772074392647482e-05</v>
+        <v>9.898283678921871e-06</v>
       </c>
       <c r="CN7" t="n">
-        <v>6.193580247781938e-06</v>
+        <v>5.307055289449636e-06</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.021613570628688e-06</v>
+        <v>2.242744085378945e-05</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.40515694511123e-05</v>
+        <v>1.081515074474737e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>8.610993063484784e-06</v>
+        <v>5.872642759641167e-06</v>
       </c>
       <c r="CR7" t="n">
-        <v>6.501071311504347e-06</v>
+        <v>1.327652512372879e-07</v>
       </c>
       <c r="CS7" t="n">
-        <v>1.02548283393844e-05</v>
+        <v>3.075421773246489e-06</v>
       </c>
       <c r="CT7" t="n">
-        <v>7.724665920250118e-06</v>
+        <v>6.449909506045515e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>3.010612999787554e-06</v>
+        <v>4.191554126009578e-06</v>
       </c>
       <c r="CV7" t="n">
-        <v>3.777927304327022e-09</v>
+        <v>5.651784249494085e-06</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.069752579496708e-05</v>
+        <v>1.313597476837458e-05</v>
       </c>
       <c r="CX7" t="n">
-        <v>7.43495593269472e-06</v>
+        <v>7.601955985592213e-06</v>
       </c>
       <c r="CY7" t="n">
-        <v>4.623851054930128e-06</v>
+        <v>9.238555321644526e-06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>3.345820914546493e-06</v>
+        <v>2.983567128467257e-06</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.482103584748984e-06</v>
+        <v>1.135946422436973e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>2.621685325721046e-06</v>
+        <v>1.854117272159783e-06</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.566107013990404e-06</v>
+        <v>4.803011051990325e-06</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.555177388785523e-06</v>
+        <v>3.351031864440301e-06</v>
       </c>
       <c r="DE7" t="n">
-        <v>6.785822279198328e-06</v>
+        <v>8.048812560446095e-06</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.070984581019729e-07</v>
+        <v>1.773723670339677e-05</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.018426701193675e-06</v>
+        <v>9.39603523875121e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>1.176372279587667e-05</v>
+        <v>1.144725501944777e-05</v>
       </c>
       <c r="DI7" t="n">
-        <v>2.139714979421115e-06</v>
+        <v>1.980738062457021e-07</v>
       </c>
       <c r="DJ7" t="n">
-        <v>7.356763035204494e-06</v>
+        <v>2.583280729595572e-05</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.925761236838298e-06</v>
+        <v>3.476946403679904e-06</v>
       </c>
       <c r="DL7" t="n">
-        <v>1.518344788564718e-06</v>
+        <v>1.680277273408137e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>5.341008090908872e-06</v>
+        <v>3.608879751482164e-06</v>
       </c>
       <c r="DN7" t="n">
-        <v>2.20800814076938e-07</v>
+        <v>1.084691211872268e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.742700075941684e-07</v>
+        <v>6.89363832862e-06</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.002061233331915e-06</v>
+        <v>7.986022865225095e-06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>5.131350917508826e-06</v>
+        <v>5.385730901252828e-07</v>
       </c>
       <c r="DR7" t="n">
-        <v>3.119450866506668e-06</v>
+        <v>2.129983158738469e-06</v>
       </c>
       <c r="DS7" t="n">
-        <v>1.690194039838389e-06</v>
+        <v>2.018502300416003e-06</v>
       </c>
       <c r="DT7" t="n">
-        <v>5.932975000177976e-06</v>
+        <v>3.946714059566148e-06</v>
       </c>
       <c r="DU7" t="n">
-        <v>2.421031013000174e-06</v>
+        <v>9.10194285097532e-06</v>
       </c>
       <c r="DV7" t="n">
-        <v>2.979154942295281e-06</v>
+        <v>4.912160875392146e-06</v>
       </c>
       <c r="DW7" t="n">
-        <v>1.325393441220513e-06</v>
+        <v>4.245424861437641e-06</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.001326927507762e-05</v>
+        <v>2.09298519848744e-07</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.352705557015724e-06</v>
+        <v>2.070490700134542e-05</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.944487616536207e-07</v>
+        <v>1.38109253384755e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>6.969748937990516e-06</v>
+        <v>2.108057515215478e-06</v>
       </c>
       <c r="EB7" t="n">
-        <v>6.319005933619337e-06</v>
+        <v>5.570203938987106e-06</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.471488755872997e-07</v>
+        <v>2.400202447461197e-06</v>
       </c>
       <c r="ED7" t="n">
-        <v>5.697535812032584e-07</v>
+        <v>1.036010962707223e-05</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.711250774860673e-06</v>
+        <v>2.042286905634683e-05</v>
       </c>
       <c r="EF7" t="n">
-        <v>3.389404355402803e-06</v>
+        <v>9.928578037943225e-06</v>
       </c>
       <c r="EG7" t="n">
-        <v>1.060245085682254e-05</v>
+        <v>4.815107786271255e-06</v>
       </c>
       <c r="EH7" t="n">
-        <v>5.880121079826495e-06</v>
+        <v>7.571641617687419e-06</v>
       </c>
       <c r="EI7" t="n">
-        <v>1.585502559464658e-06</v>
+        <v>3.158281515425188e-06</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1.527667905065755e-06</v>
+        <v>3.059190248677623e-06</v>
       </c>
       <c r="EK7" t="n">
-        <v>8.417545700467599e-07</v>
+        <v>7.419071152980905e-06</v>
       </c>
       <c r="EL7" t="n">
-        <v>4.185237230558414e-06</v>
+        <v>2.128839753368084e-07</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.119382204706199e-06</v>
+        <v>1.028266183311644e-06</v>
       </c>
       <c r="EN7" t="n">
-        <v>2.437983994241222e-06</v>
+        <v>2.320001158295781e-06</v>
       </c>
       <c r="EO7" t="n">
-        <v>7.558446668554097e-08</v>
+        <v>3.910069608537015e-06</v>
       </c>
       <c r="EP7" t="n">
-        <v>4.809285201190505e-06</v>
+        <v>8.381975021620747e-06</v>
       </c>
       <c r="EQ7" t="n">
-        <v>6.94711752657895e-06</v>
+        <v>6.617076905968133e-06</v>
       </c>
       <c r="ER7" t="n">
-        <v>4.734643880510703e-06</v>
+        <v>3.208405132681946e-07</v>
       </c>
       <c r="ES7" t="n">
-        <v>5.085402790427906e-06</v>
+        <v>7.098030891938834e-06</v>
       </c>
       <c r="ET7" t="n">
-        <v>6.666894478257746e-06</v>
+        <v>4.38903089161613e-06</v>
       </c>
       <c r="EU7" t="n">
-        <v>1.046196121023968e-05</v>
+        <v>1.994017793549574e-06</v>
       </c>
       <c r="EV7" t="n">
-        <v>1.258402971870964e-05</v>
+        <v>5.773712473455817e-06</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.723757122817915e-06</v>
+        <v>4.645524768420728e-06</v>
       </c>
       <c r="EX7" t="n">
-        <v>1.991682438529097e-06</v>
+        <v>5.213650183577556e-06</v>
       </c>
       <c r="EY7" t="n">
-        <v>1.076928765542107e-05</v>
+        <v>1.556594543217216e-05</v>
       </c>
       <c r="EZ7" t="n">
-        <v>5.842847713211086e-06</v>
+        <v>4.572669240587857e-06</v>
       </c>
       <c r="FA7" t="n">
-        <v>2.756795765890274e-06</v>
+        <v>1.161253567261156e-05</v>
       </c>
       <c r="FB7" t="n">
-        <v>1.715293592496892e-06</v>
+        <v>8.367082955373917e-07</v>
       </c>
       <c r="FC7" t="n">
-        <v>1.840656750573544e-06</v>
+        <v>9.243028216587845e-06</v>
       </c>
       <c r="FD7" t="n">
-        <v>4.611987606040202e-06</v>
+        <v>3.396772626729216e-06</v>
       </c>
       <c r="FE7" t="n">
-        <v>9.193475989377475e-07</v>
+        <v>4.757293027068954e-06</v>
       </c>
       <c r="FF7" t="n">
-        <v>4.262322818249231e-06</v>
+        <v>1.261479809500088e-07</v>
       </c>
       <c r="FG7" t="n">
-        <v>2.13850717045716e-06</v>
+        <v>1.703166162769776e-06</v>
       </c>
       <c r="FH7" t="n">
-        <v>1.411214839208697e-06</v>
+        <v>1.63583827088587e-05</v>
       </c>
       <c r="FI7" t="n">
-        <v>7.380622264463454e-06</v>
+        <v>1.375866122543812e-05</v>
       </c>
       <c r="FJ7" t="n">
-        <v>7.018216365395347e-06</v>
+        <v>1.226695439981995e-05</v>
       </c>
       <c r="FK7" t="n">
-        <v>3.756010755751049e-06</v>
+        <v>1.009712286759168e-05</v>
       </c>
       <c r="FL7" t="n">
-        <v>1.581991227794788e-06</v>
+        <v>1.252833681064658e-05</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.233543912348978e-06</v>
+        <v>6.237250090634916e-06</v>
       </c>
       <c r="FN7" t="n">
-        <v>5.504133696376812e-06</v>
+        <v>1.338971833320102e-05</v>
       </c>
       <c r="FO7" t="n">
-        <v>6.618979568884242e-06</v>
+        <v>1.799164601834491e-05</v>
       </c>
       <c r="FP7" t="n">
-        <v>6.897923412907403e-06</v>
+        <v>1.420465650880942e-05</v>
       </c>
       <c r="FQ7" t="n">
-        <v>1.080573292711051e-05</v>
+        <v>2.668202250788454e-05</v>
       </c>
       <c r="FR7" t="n">
-        <v>4.946325134369545e-06</v>
+        <v>8.222143151215278e-06</v>
       </c>
       <c r="FS7" t="n">
-        <v>3.677687345771119e-07</v>
+        <v>2.462005795678124e-05</v>
       </c>
       <c r="FT7" t="n">
-        <v>4.241483111400157e-06</v>
+        <v>3.640698423623689e-06</v>
       </c>
       <c r="FU7" t="n">
-        <v>4.845410899179114e-07</v>
+        <v>5.464009973366046e-07</v>
       </c>
       <c r="FV7" t="n">
-        <v>8.627286661067046e-06</v>
+        <v>5.491288447956322e-06</v>
       </c>
       <c r="FW7" t="n">
-        <v>4.143508249399019e-06</v>
+        <v>2.098922595905606e-05</v>
       </c>
       <c r="FX7" t="n">
-        <v>2.142174480468384e-06</v>
+        <v>4.846067895414308e-06</v>
       </c>
       <c r="FY7" t="n">
-        <v>1.064427669916768e-05</v>
+        <v>2.763765678537311e-07</v>
       </c>
       <c r="FZ7" t="n">
-        <v>3.484748276605387e-06</v>
+        <v>3.67092411579506e-06</v>
       </c>
       <c r="GA7" t="n">
-        <v>9.443907629247406e-07</v>
+        <v>1.645462543820031e-05</v>
       </c>
       <c r="GB7" t="n">
-        <v>2.231590315204812e-06</v>
+        <v>1.169667484646197e-05</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.645714064579806e-06</v>
+        <v>2.710925582505297e-05</v>
       </c>
       <c r="GD7" t="n">
-        <v>7.346472557401285e-06</v>
+        <v>1.204368982143933e-05</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.817569136619568e-05</v>
+        <v>6.18944159214152e-06</v>
       </c>
       <c r="GF7" t="n">
-        <v>3.152479166601552e-06</v>
+        <v>2.595942021343944e-07</v>
       </c>
       <c r="GG7" t="n">
-        <v>4.46915464635822e-08</v>
+        <v>4.15589192925836e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.001262336620129645</v>
+        <v>1.176534897240344e-05</v>
       </c>
       <c r="B8" t="n">
-        <v>0.009661934338510036</v>
+        <v>0.000190724793355912</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001137838931754231</v>
+        <v>6.785512232454494e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005115729290992022</v>
+        <v>4.573597834678367e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002206344623118639</v>
+        <v>8.960651030065492e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007876371964812279</v>
+        <v>0.0002310244017280638</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002440199605189264</v>
+        <v>2.214194864791352e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002587425988167524</v>
+        <v>8.096872625174001e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006925777997821569</v>
+        <v>5.334185334504582e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002415868453681469</v>
+        <v>2.690711335162632e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008748840540647507</v>
+        <v>0.0002057501988019794</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004593382473103702</v>
+        <v>0.0001023738950607367</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004066966474056244</v>
+        <v>0.0001249186461791396</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000378375087166205</v>
+        <v>8.215651905629784e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007809939794242382</v>
+        <v>0.000275900267297402</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0008500122930854559</v>
+        <v>1.736667218210641e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001337251276709139</v>
+        <v>2.979796408908442e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0005354876630008221</v>
+        <v>5.49854121345561e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0002043638669420034</v>
+        <v>3.591801942093298e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0008448511362075806</v>
+        <v>2.994100395881105e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0006786928861401975</v>
+        <v>6.425585524993949e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001890822779387236</v>
+        <v>3.793649739236571e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0006766211008653045</v>
+        <v>3.082893090322614e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0004424532235134393</v>
+        <v>4.162401091889478e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0005774400196969509</v>
+        <v>3.50872433045879e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001034335698932409</v>
+        <v>3.262965037720278e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009373283246532083</v>
+        <v>2.960638266813476e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.519752347841859e-05</v>
+        <v>4.123873804928735e-05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0003313633787911385</v>
+        <v>1.370086465612985e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0002590938820503652</v>
+        <v>4.697082476923242e-05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0003026461927220225</v>
+        <v>7.145319250412285e-05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0003329901664983481</v>
+        <v>8.596793486503884e-05</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0001466042886022478</v>
+        <v>7.204309804365039e-05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0002077613025903702</v>
+        <v>1.088682529370999e-05</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0004404545179568231</v>
+        <v>0.0001248438347829506</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0007529488066211343</v>
+        <v>1.378259094053647e-05</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.00124682579189539</v>
+        <v>3.727353032445535e-05</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001085959607735276</v>
+        <v>3.499026934150606e-05</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0004018461622763425</v>
+        <v>2.621980638650712e-05</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.00022456597071141</v>
+        <v>2.132414010702632e-05</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0001655914384173229</v>
+        <v>2.236456748505589e-05</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.00124820414930582</v>
+        <v>3.293002737336792e-05</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0002399943768978119</v>
+        <v>1.089445686375257e-05</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0009266930865123868</v>
+        <v>3.291567190899514e-05</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001631427672691643</v>
+        <v>4.611632903106511e-06</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0004506762488745153</v>
+        <v>3.240083242417313e-05</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.005702744703739882</v>
+        <v>0.0001690860517555848</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0003155012091156095</v>
+        <v>6.443883466999978e-05</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001369105069898069</v>
+        <v>3.350227780174464e-05</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001957042375579476</v>
+        <v>0.0001110593875637278</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.004119083750993013</v>
+        <v>0.0002086299355141819</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0005847109132446349</v>
+        <v>1.320681712968508e-05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0008449595188722014</v>
+        <v>3.989600008935668e-05</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.002380417427048087</v>
+        <v>6.842974471510388e-07</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.001041031908243895</v>
+        <v>4.181088661425747e-05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.002075706841424108</v>
+        <v>1.642181086936034e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.003014791756868362</v>
+        <v>5.31088408024516e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0007898258045315742</v>
+        <v>3.413769445614889e-05</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001560700475238264</v>
+        <v>6.341529660858214e-05</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.002069941023364663</v>
+        <v>4.095649273949675e-05</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0002038587699644268</v>
+        <v>3.47704190062359e-05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001188353751786053</v>
+        <v>6.668450077995658e-05</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.000573659548535943</v>
+        <v>1.347217494185315e-05</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0002372901944909245</v>
+        <v>3.628293598012533e-06</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.002170799998566508</v>
+        <v>7.632839697180316e-05</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001130448654294014</v>
+        <v>2.432833025522996e-05</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001003439188934863</v>
+        <v>2.949483314296231e-05</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0001149793388321996</v>
+        <v>4.418385651661083e-05</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0004424377693794668</v>
+        <v>2.448366467433516e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0007696942775510252</v>
+        <v>3.140354965580627e-05</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0008653452387079597</v>
+        <v>2.867491457436699e-05</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0003168309922330081</v>
+        <v>3.350558108650148e-05</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0001337485737167299</v>
+        <v>2.034812678175513e-05</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.003169102827087045</v>
+        <v>7.987535354914144e-05</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001117586507461965</v>
+        <v>9.86646773526445e-06</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001427526469342411</v>
+        <v>1.450675699743442e-05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0008688075467944145</v>
+        <v>2.184888944611885e-05</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.00182872568257153</v>
+        <v>0.0001032688160194084</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0005365012330003083</v>
+        <v>6.751187174813822e-05</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.000609087641350925</v>
+        <v>2.13466992136091e-05</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001239573117345572</v>
+        <v>1.948064164025709e-05</v>
       </c>
       <c r="CD8" t="n">
-        <v>7.95711821410805e-05</v>
+        <v>5.913010681979358e-06</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001583166187629104</v>
+        <v>6.473403482232243e-05</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001087046344764531</v>
+        <v>2.0559826225508e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0007728944765403867</v>
+        <v>6.907588613103144e-06</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0003563596110325307</v>
+        <v>1.97761801246088e-05</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001121006091125309</v>
+        <v>5.355639950721525e-05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0004688556655310094</v>
+        <v>4.274073944543488e-06</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0005395675543695688</v>
+        <v>9.741192116052844e-06</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.000829744094517082</v>
+        <v>3.288639618403977e-06</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.002003158675506711</v>
+        <v>3.618637128965929e-05</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0003847673069685698</v>
+        <v>2.994807982759085e-05</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0002054646902251989</v>
+        <v>6.991795817157254e-05</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.001279440592043102</v>
+        <v>3.974780338467099e-05</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0004377763252705336</v>
+        <v>3.213817035430111e-05</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.001364591880701482</v>
+        <v>1.025862047754345e-06</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.001788937603123486</v>
+        <v>6.126409425633028e-05</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.001312796375714242</v>
+        <v>7.185624417616054e-05</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0002979422570206225</v>
+        <v>2.449371640977915e-05</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0001131794342654757</v>
+        <v>1.287678423977923e-05</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.001459967461414635</v>
+        <v>5.672928818967193e-05</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.001088704215362668</v>
+        <v>3.039982402697206e-05</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.001244899816811085</v>
+        <v>2.091112219204661e-05</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0001604087010491639</v>
+        <v>2.117291296599433e-05</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.001182687468826771</v>
+        <v>6.846606265753508e-05</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0004528877325356007</v>
+        <v>6.61110379951424e-06</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001190702780149877</v>
+        <v>1.489555143052712e-05</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0004948582500219345</v>
+        <v>1.009439984045457e-05</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0008410731097683311</v>
+        <v>1.067894299922045e-05</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0005581943551078439</v>
+        <v>0.0001050454520736821</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0002758389455266297</v>
+        <v>9.007474727695808e-05</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.002540759509429336</v>
+        <v>5.08731318404898e-05</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.002013631165027618</v>
+        <v>2.068892354145646e-05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.001009956002235413</v>
+        <v>6.34799143881537e-05</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0008523082360625267</v>
+        <v>2.35330098803388e-05</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.001619074493646622</v>
+        <v>0.0001033984444802627</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.002077492419630289</v>
+        <v>2.729559673753101e-05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0003913467517122626</v>
+        <v>2.317578400834464e-05</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0006327916053123772</v>
+        <v>6.10471106483601e-05</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.000508272263687104</v>
+        <v>5.982529728498776e-06</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0002608047216199338</v>
+        <v>4.528548015514389e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0002745356177911162</v>
+        <v>1.335834076598985e-05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0007194365607574582</v>
+        <v>4.290189463063143e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>4.62621683254838e-05</v>
+        <v>2.547904659877531e-05</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.000177702255314216</v>
+        <v>8.024177805054933e-05</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0009171984856948256</v>
+        <v>3.051913517992944e-05</v>
       </c>
       <c r="DW8" t="n">
-        <v>1.053899177350104e-05</v>
+        <v>7.578461008961312e-06</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0007883632788434625</v>
+        <v>3.111052501481026e-05</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001252955989912152</v>
+        <v>7.416940934490412e-05</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0002576766128186136</v>
+        <v>1.037591027852613e-05</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0007530755246989429</v>
+        <v>6.343098357319832e-05</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0006637683254666626</v>
+        <v>1.503489329479635e-06</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0003865164762828499</v>
+        <v>5.950136255705729e-05</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0005457078805193305</v>
+        <v>5.127948679728433e-05</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0005774869932793081</v>
+        <v>7.568468572571874e-05</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0009234979515895247</v>
+        <v>4.491639629122801e-07</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.001565340324304998</v>
+        <v>9.285744454246014e-06</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.001287831808440387</v>
+        <v>1.650983904255554e-06</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0005183105240575969</v>
+        <v>1.921116017911118e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0003899526782333851</v>
+        <v>2.062406565528363e-07</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.001107158255763352</v>
+        <v>1.43487959576305e-05</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0005150958313606679</v>
+        <v>1.100990812119562e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>3.700777233461849e-05</v>
+        <v>8.516336492903065e-06</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0002171375672332942</v>
+        <v>3.900511364918202e-05</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0001056049077305943</v>
+        <v>5.11596863361774e-06</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0008529387996532023</v>
+        <v>4.169646126683801e-05</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0009233050514012575</v>
+        <v>1.483978667238262e-05</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0007550169248133898</v>
+        <v>3.630930950748734e-05</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0007185913273133337</v>
+        <v>3.17899466608651e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0007237246027216315</v>
+        <v>3.316205766168423e-05</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.001427470706403255</v>
+        <v>6.857212611066643e-06</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.002819341840222478</v>
+        <v>6.557901087944629e-06</v>
       </c>
       <c r="EW8" t="n">
-        <v>4.855995939578861e-05</v>
+        <v>1.428249561286066e-05</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0003255944466218352</v>
+        <v>3.586422053558636e-06</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.001361800357699394</v>
+        <v>6.886578921694309e-05</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0009050183580256999</v>
+        <v>1.493766831117682e-05</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0009598276810720563</v>
+        <v>2.120505087077618e-05</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0002025730209425092</v>
+        <v>1.794060881366022e-05</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0009507127106189728</v>
+        <v>5.857413998455741e-05</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0008009575540199876</v>
+        <v>1.488075668021338e-05</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0008456883952021599</v>
+        <v>1.301229531236459e-05</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0008897697553038597</v>
+        <v>1.969560798897874e-05</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0005745220114476979</v>
+        <v>1.036192225001287e-05</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0003296818467788398</v>
+        <v>2.271817356813699e-05</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.001009190338663757</v>
+        <v>4.377521690912545e-05</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.001396420528180897</v>
+        <v>3.651291262940504e-05</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0001225285086547956</v>
+        <v>6.246240445761941e-06</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.001672962098382413</v>
+        <v>8.608360076323152e-05</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0001579473610036075</v>
+        <v>8.856927706801798e-06</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.001367070130072534</v>
+        <v>7.444724906235933e-05</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0005967621691524982</v>
+        <v>0.0001050477003445849</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.001099121640436351</v>
+        <v>4.714870374300517e-05</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0004439441254362464</v>
+        <v>3.42714847647585e-05</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.001182326930575073</v>
+        <v>2.128240885213017e-05</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0009616022580303252</v>
+        <v>4.767888458445668e-05</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.00197669630870223</v>
+        <v>4.362792606116273e-05</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0006098399171605706</v>
+        <v>1.556925599288661e-05</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0007972255116328597</v>
+        <v>3.145862137898803e-05</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0006111626280471683</v>
+        <v>0.0001799963065423071</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0003284628037363291</v>
+        <v>9.757028237800114e-06</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.001910345163196325</v>
+        <v>2.864672205760144e-05</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0007030172855593264</v>
+        <v>1.316061934630852e-05</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0008516709785908461</v>
+        <v>8.161865844158456e-05</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0004289283533580601</v>
+        <v>1.553601396153681e-05</v>
       </c>
       <c r="GC8" t="n">
-        <v>1.254247035831213e-05</v>
+        <v>9.606897947378457e-05</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0007918815826997161</v>
+        <v>5.485339715960436e-05</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.003811905393376946</v>
+        <v>4.007260577054694e-05</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0001109155709855258</v>
+        <v>1.470292772864923e-05</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0007947348640300333</v>
+        <v>1.137496838055085e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.154007936245762e-05</v>
+        <v>2.898880495649792e-07</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003020618809387088</v>
+        <v>1.50905418649927e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>9.253462485503405e-05</v>
+        <v>1.470341430831468e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001271709450520575</v>
+        <v>1.212773895531427e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009765085997059941</v>
+        <v>3.791843710132525e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001236313953995705</v>
+        <v>1.072073700925102e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002059104444924742</v>
+        <v>5.375883347369381e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0003643459058366716</v>
+        <v>3.353367219460779e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006685431580990553</v>
+        <v>2.414055586541508e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>4.260525020072237e-05</v>
+        <v>1.201444348453151e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003305448684841394</v>
+        <v>1.785969061529613e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002511835482437164</v>
+        <v>4.93805828227778e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0006049439543858171</v>
+        <v>2.04590992325393e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0004060241917613894</v>
+        <v>1.583889343237388e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0008705234504304826</v>
+        <v>1.392848730574769e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001108773140003905</v>
+        <v>3.032293705018674e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001024712400976568</v>
+        <v>4.054499527228472e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0004853454593103379</v>
+        <v>2.328782215954561e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>6.619944178964943e-05</v>
+        <v>2.636951990098169e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0003628839622251689</v>
+        <v>3.218073914013075e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0002863466506823897</v>
+        <v>1.140394587650917e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0003444900503382087</v>
+        <v>5.437200911728723e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003023499739356339</v>
+        <v>6.996139632065024e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>7.812253898009658e-06</v>
+        <v>5.48192019778071e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2111002181191e-05</v>
+        <v>3.010366071976023e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0001847019884735346</v>
+        <v>2.80489814485918e-07</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0002647751243785024</v>
+        <v>3.824542034180922e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0001543731632409617</v>
+        <v>2.402600216555584e-07</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.779980710940436e-05</v>
+        <v>8.140486329466512e-08</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0005066767917014658</v>
+        <v>3.921208246993046e-08</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.000164739933097735</v>
+        <v>4.231881973737472e-07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.639910442463588e-05</v>
+        <v>1.797702964267955e-07</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0002530379570089281</v>
+        <v>7.152937087084865e-07</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0002287588285980746</v>
+        <v>1.597659604613e-07</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.152131416252814e-05</v>
+        <v>9.601711781215272e-07</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0002161615993827581</v>
+        <v>2.205530336141237e-07</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0003760622930712998</v>
+        <v>2.883872980419255e-07</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0004677804827224463</v>
+        <v>2.983120452881849e-07</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0003616465837694705</v>
+        <v>8.788953209659667e-08</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.075910353800282e-05</v>
+        <v>4.104924187231518e-07</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.285146421054378e-05</v>
+        <v>1.559368172365794e-07</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0002705041843000799</v>
+        <v>1.328729553051744e-07</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.558838842669502e-05</v>
+        <v>5.507497746748413e-08</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.107640077359974e-05</v>
+        <v>4.575915966142929e-07</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.248192974249832e-05</v>
+        <v>2.025790166726438e-07</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0003285031707491726</v>
+        <v>4.343925468219823e-07</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.001904357573948801</v>
+        <v>1.622951231183833e-06</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.000550213095266372</v>
+        <v>2.215131331695375e-07</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0004622932174243033</v>
+        <v>6.027732410984754e-07</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.426162245683372e-05</v>
+        <v>1.196831931338238e-06</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0005986219039186835</v>
+        <v>8.156503099598922e-07</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0002562028530519456</v>
+        <v>1.437399532733252e-09</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.705000411486253e-05</v>
+        <v>1.886809855022875e-07</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0001792765688151121</v>
+        <v>4.622212657068303e-08</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.989325189962983e-05</v>
+        <v>2.019692715293786e-07</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0005167075432837009</v>
+        <v>2.349976568893908e-07</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0003101477341260761</v>
+        <v>4.604698915500194e-07</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.302352555096149e-05</v>
+        <v>2.577899067546241e-07</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0008776306640356779</v>
+        <v>8.067780186138407e-07</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0004087879788130522</v>
+        <v>3.702883759615361e-07</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0001671455829637125</v>
+        <v>3.482776378405106e-07</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.898647840600461e-05</v>
+        <v>5.957127200417744e-07</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0001447071554139256</v>
+        <v>4.823579047297244e-07</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0003889420186169446</v>
+        <v>1.636780950775574e-07</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0003420366847421974</v>
+        <v>3.858463628603204e-07</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.637664384674281e-05</v>
+        <v>1.099181758945633e-07</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0001047877158271149</v>
+        <v>3.582444776384364e-07</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0004818324232473969</v>
+        <v>1.243796532435226e-07</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.288995503680781e-05</v>
+        <v>1.968355576309477e-07</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0001526110572740436</v>
+        <v>5.486135705723427e-07</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0001198680329252966</v>
+        <v>4.586427948538585e-08</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.934565367875621e-05</v>
+        <v>3.128842820387945e-07</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0002560457214713097</v>
+        <v>2.308646571691497e-07</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.001197814592160285</v>
+        <v>8.961575304056169e-07</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0002580387517809868</v>
+        <v>3.885447341644976e-08</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.000354103627614677</v>
+        <v>9.251862138626166e-07</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0001032651925925165</v>
+        <v>5.522638275579084e-07</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.761440504807979e-05</v>
+        <v>8.647267577543971e-07</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001165788926300593</v>
+        <v>2.864878183572728e-07</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.098143472219817e-05</v>
+        <v>4.020645860691729e-08</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.708682950469665e-05</v>
+        <v>1.305486847513748e-07</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0001187410816783085</v>
+        <v>6.605115743241186e-08</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0005096847307868302</v>
+        <v>4.848778303312429e-07</v>
       </c>
       <c r="CF9" t="n">
-        <v>4.353394615463912e-06</v>
+        <v>1.458996212733155e-08</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0001712785160634667</v>
+        <v>3.567679982552363e-07</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.831218105508015e-05</v>
+        <v>1.687771629121926e-07</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0002359038626309484</v>
+        <v>2.212136109847052e-07</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0002256758016301319</v>
+        <v>8.281202923399178e-08</v>
       </c>
       <c r="CK9" t="n">
-        <v>3.782721614697948e-05</v>
+        <v>1.056719014513874e-07</v>
       </c>
       <c r="CL9" t="n">
-        <v>9.030882938532159e-05</v>
+        <v>1.400215268176908e-07</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0009177927859127522</v>
+        <v>6.54354437301663e-09</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0002352926530875266</v>
+        <v>4.597703195940994e-07</v>
       </c>
       <c r="CO9" t="n">
-        <v>5.345788667909801e-05</v>
+        <v>6.535836973853293e-07</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0004700124554801732</v>
+        <v>9.659299848863157e-07</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0004433113208506256</v>
+        <v>2.235688612017839e-08</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.000413755071349442</v>
+        <v>6.538232355524087e-07</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.000621770101133734</v>
+        <v>2.075061900086439e-07</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0003782936837524176</v>
+        <v>5.093795607535867e-07</v>
       </c>
       <c r="CU9" t="n">
-        <v>2.672717528184876e-05</v>
+        <v>1.757848480110624e-07</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.012284676311538e-05</v>
+        <v>1.135195191181992e-07</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0005295936716720462</v>
+        <v>5.225188601798436e-07</v>
       </c>
       <c r="CX9" t="n">
-        <v>2.398141077719629e-05</v>
+        <v>6.532343377330108e-08</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.000257513951510191</v>
+        <v>4.66334626025855e-07</v>
       </c>
       <c r="CZ9" t="n">
-        <v>3.839945566141978e-05</v>
+        <v>1.995248055663978e-07</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0002626563364174217</v>
+        <v>2.935186103059095e-07</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0002335790341021493</v>
+        <v>4.649306362125571e-08</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0001634112413739786</v>
+        <v>9.336161355122385e-08</v>
       </c>
       <c r="DD9" t="n">
-        <v>6.424897583201528e-05</v>
+        <v>1.350393006305239e-07</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0004243587027303874</v>
+        <v>1.066480947997661e-08</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0005040185642428696</v>
+        <v>5.110177880851552e-07</v>
       </c>
       <c r="DG9" t="n">
-        <v>9.836935350904241e-05</v>
+        <v>1.27537930438848e-07</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0006241811788640916</v>
+        <v>1.789554744391353e-07</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0008721348713152111</v>
+        <v>2.432535666230251e-07</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0002126124745700508</v>
+        <v>3.532613845891319e-07</v>
       </c>
       <c r="DK9" t="n">
-        <v>9.992615377996117e-05</v>
+        <v>2.472168603162572e-07</v>
       </c>
       <c r="DL9" t="n">
-        <v>9.494768892182037e-05</v>
+        <v>7.067555429784989e-07</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0003047462669201195</v>
+        <v>1.652994257028695e-07</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0002108120243065059</v>
+        <v>2.81941197499691e-07</v>
       </c>
       <c r="DO9" t="n">
-        <v>4.184039426036179e-05</v>
+        <v>1.988885287573794e-07</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0001278620620723814</v>
+        <v>7.367795973323155e-08</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0001634204381844029</v>
+        <v>3.046228869152401e-07</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0001481257932027802</v>
+        <v>2.123773867879208e-07</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0001494480529800057</v>
+        <v>6.694985899002859e-08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0001356675929855555</v>
+        <v>3.054948649605649e-07</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0002144571917597204</v>
+        <v>5.280094228510279e-07</v>
       </c>
       <c r="DV9" t="n">
-        <v>5.424184200819582e-05</v>
+        <v>1.860884140114649e-07</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0002714729635044932</v>
+        <v>5.830151650343396e-08</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0003757056838367134</v>
+        <v>1.979227448600795e-08</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0001365071511827409</v>
+        <v>4.519657466062199e-07</v>
       </c>
       <c r="DZ9" t="n">
-        <v>6.404293526429683e-05</v>
+        <v>4.695315567460057e-07</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0001656376261962578</v>
+        <v>3.924765223928262e-07</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.000205107731744647</v>
+        <v>5.78375676241194e-08</v>
       </c>
       <c r="EC9" t="n">
-        <v>7.736462430329993e-05</v>
+        <v>3.354644206865487e-08</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0003070062957704067</v>
+        <v>5.438364496512804e-07</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0003654938191175461</v>
+        <v>3.506063421809813e-07</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0002767424448393285</v>
+        <v>1.588421127962647e-07</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0005674554849974811</v>
+        <v>2.223525825684192e-07</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0001351623795926571</v>
+        <v>2.686450955025066e-07</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0002193095133407041</v>
+        <v>2.758733899099752e-07</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0001123516485677101</v>
+        <v>1.004908014579087e-07</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0001864387159002945</v>
+        <v>1.16992858067988e-07</v>
       </c>
       <c r="EL9" t="n">
-        <v>8.799038914730772e-05</v>
+        <v>1.133648623863337e-07</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0002204358170274645</v>
+        <v>3.672422721479052e-08</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0001797623262973502</v>
+        <v>1.203561623697169e-07</v>
       </c>
       <c r="EO9" t="n">
-        <v>5.352267908165231e-05</v>
+        <v>1.068220001343434e-08</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0005827274871990085</v>
+        <v>3.964835855185811e-07</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0001633526117075235</v>
+        <v>5.341900077837636e-08</v>
       </c>
       <c r="ER9" t="n">
-        <v>9.458250860916451e-05</v>
+        <v>4.171935188423959e-07</v>
       </c>
       <c r="ES9" t="n">
-        <v>4.788495789398439e-05</v>
+        <v>1.079541505077941e-07</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0001228972541866824</v>
+        <v>2.414431321540178e-07</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0003191624418832362</v>
+        <v>1.495766639436624e-07</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0004008247924502939</v>
+        <v>2.061840120859415e-07</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0001568797160871327</v>
+        <v>2.998456238856306e-07</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.00013331750233192</v>
+        <v>9.82029959573083e-08</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0005169837386347353</v>
+        <v>5.453002245303651e-07</v>
       </c>
       <c r="EZ9" t="n">
-        <v>7.46703808545135e-05</v>
+        <v>1.320240450297661e-08</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0001381658366881311</v>
+        <v>5.406576519817463e-07</v>
       </c>
       <c r="FB9" t="n">
-        <v>9.132461855188012e-05</v>
+        <v>1.245439023023209e-07</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.00026294807321392</v>
+        <v>2.316346865427477e-07</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0001970095472643152</v>
+        <v>1.522938362086279e-07</v>
       </c>
       <c r="FE9" t="n">
-        <v>6.64524341118522e-05</v>
+        <v>7.498490361967924e-08</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0001053125815815292</v>
+        <v>3.407545889899666e-08</v>
       </c>
       <c r="FG9" t="n">
-        <v>2.250480247312225e-05</v>
+        <v>1.598215391140911e-07</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0002724576334003359</v>
+        <v>5.526662789634429e-07</v>
       </c>
       <c r="FI9" t="n">
-        <v>7.402850314974785e-07</v>
+        <v>3.437917825976911e-07</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0004695548850577325</v>
+        <v>3.950972597976943e-07</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0001182839623652399</v>
+        <v>1.914633571686863e-07</v>
       </c>
       <c r="FL9" t="n">
-        <v>5.211011739447713e-05</v>
+        <v>3.79200514544209e-07</v>
       </c>
       <c r="FM9" t="n">
-        <v>9.079337905859575e-05</v>
+        <v>1.696749336588255e-07</v>
       </c>
       <c r="FN9" t="n">
-        <v>8.457253716187552e-05</v>
+        <v>2.078356260426517e-07</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0002183107571909204</v>
+        <v>5.669434699484555e-07</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0004524762043729424</v>
+        <v>6.521219120259047e-07</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0001502037775935605</v>
+        <v>9.592705509930965e-07</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.000242030102526769</v>
+        <v>5.258562509879994e-07</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0001799061865312979</v>
+        <v>6.463136514867074e-07</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0006446424522437155</v>
+        <v>1.053188753985523e-07</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0001728101051412523</v>
+        <v>2.368910685390802e-07</v>
       </c>
       <c r="FV9" t="n">
-        <v>2.58317231782712e-06</v>
+        <v>2.690257616677627e-08</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0005130653153173625</v>
+        <v>5.1327742767171e-07</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0001696539984550327</v>
+        <v>1.245157505991301e-07</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0002389492583461106</v>
+        <v>1.025309046553957e-07</v>
       </c>
       <c r="FZ9" t="n">
-        <v>4.935117613058537e-05</v>
+        <v>1.445124411247889e-07</v>
       </c>
       <c r="GA9" t="n">
-        <v>7.213476055767387e-05</v>
+        <v>4.489302227739245e-07</v>
       </c>
       <c r="GB9" t="n">
-        <v>3.197619662387297e-05</v>
+        <v>3.079950374740292e-07</v>
       </c>
       <c r="GC9" t="n">
-        <v>8.49883581395261e-05</v>
+        <v>8.423472195318027e-07</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0002223863557446748</v>
+        <v>6.844662721050554e-07</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.0002044743159785867</v>
+        <v>2.617894665490894e-07</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0001007772516459227</v>
+        <v>1.362474648658463e-07</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0004244530573487282</v>
+        <v>1.213606548589041e-09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.404329569298923e-10</v>
+        <v>1.324927545454102e-08</v>
       </c>
       <c r="B10" t="n">
-        <v>3.067326115324676e-10</v>
+        <v>3.805464743322773e-08</v>
       </c>
       <c r="C10" t="n">
-        <v>3.180342100783662e-11</v>
+        <v>2.422522182854436e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>3.47001843925554e-10</v>
+        <v>1.429565976707181e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>2.039000912557043e-10</v>
+        <v>5.130284641552407e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>8.185964059381767e-12</v>
+        <v>3.967794981463157e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>1.203642324698606e-10</v>
+        <v>2.430693424315677e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>4.170527811986346e-11</v>
+        <v>2.045484848167689e-08</v>
       </c>
       <c r="I10" t="n">
-        <v>1.105412220092639e-10</v>
+        <v>4.045095369775709e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>1.476201938466204e-10</v>
+        <v>1.407895577898444e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>2.052874537028515e-10</v>
+        <v>4.41626326619371e-08</v>
       </c>
       <c r="L10" t="n">
-        <v>5.360681343269391e-11</v>
+        <v>8.416328078908464e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>1.301074942228198e-10</v>
+        <v>2.910710428238872e-08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.63157523550106e-10</v>
+        <v>2.123370634876665e-08</v>
       </c>
       <c r="O10" t="n">
-        <v>2.059500070483722e-10</v>
+        <v>4.561968935945515e-08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.609221922382886e-10</v>
+        <v>2.884066319097656e-09</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.228768198302532e-10</v>
+        <v>1.106903724235053e-08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27855670495336e-10</v>
+        <v>6.022141452177721e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>9.583000191992763e-12</v>
+        <v>5.512343470570613e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>1.257035170398879e-10</v>
+        <v>1.813625694069287e-09</v>
       </c>
       <c r="U10" t="n">
-        <v>3.248154176183071e-11</v>
+        <v>3.632020018073945e-09</v>
       </c>
       <c r="V10" t="n">
-        <v>8.287366452808254e-12</v>
+        <v>9.845262383123554e-09</v>
       </c>
       <c r="W10" t="n">
-        <v>2.169614210512094e-10</v>
+        <v>3.919690350073779e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.036208341353984e-10</v>
+        <v>2.579345403930233e-09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.357373657917549e-10</v>
+        <v>5.720152795873901e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.969369459176029e-11</v>
+        <v>6.812612696194265e-09</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.968199793901732e-11</v>
+        <v>7.050261485730402e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.494689342937619e-12</v>
+        <v>1.706660146538752e-09</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.230326919462684e-11</v>
+        <v>1.314860664791695e-08</v>
       </c>
       <c r="AD10" t="n">
-        <v>7.907613452928786e-11</v>
+        <v>2.581034275195293e-09</v>
       </c>
       <c r="AE10" t="n">
-        <v>7.298632531682614e-11</v>
+        <v>5.869591035434496e-09</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.164471019610147e-10</v>
+        <v>1.704018792736406e-08</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.466142394463855e-11</v>
+        <v>2.034528989725004e-08</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.307322719667496e-11</v>
+        <v>2.957919242874141e-09</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.49747010466961e-12</v>
+        <v>2.926126718705291e-08</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.120198362518202e-11</v>
+        <v>1.394540483090623e-09</v>
       </c>
       <c r="AK10" t="n">
-        <v>7.409735325314415e-11</v>
+        <v>8.880986612780362e-09</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.480947210505626e-11</v>
+        <v>9.147404611553611e-09</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.500424256008827e-11</v>
+        <v>1.258002146897752e-08</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.963709131222682e-12</v>
+        <v>6.949192776772861e-09</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.19364682668699e-11</v>
+        <v>5.587664553274863e-09</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.79807027442547e-11</v>
+        <v>4.146520016234945e-09</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.25421434191442e-11</v>
+        <v>4.236934358914368e-09</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.013704120644832e-10</v>
+        <v>6.546553077413364e-09</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.563040223448667e-11</v>
+        <v>5.205500919203132e-09</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.434564438409282e-11</v>
+        <v>9.990626992362195e-09</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.617019157462707e-10</v>
+        <v>3.633414635828558e-08</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.713860303675929e-11</v>
+        <v>1.461458154494721e-08</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.67395028394246e-10</v>
+        <v>8.26430923694943e-10</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.884001702012199e-11</v>
+        <v>3.885589450192128e-08</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.071736946029361e-11</v>
+        <v>3.596379372083902e-08</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.746028751610119e-11</v>
+        <v>6.555322951129483e-09</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.808584070485459e-12</v>
+        <v>1.06649666875569e-09</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.31049293481145e-11</v>
+        <v>1.446576636254804e-09</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.129201313154198e-11</v>
+        <v>1.486056167010474e-09</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.231458239356556e-11</v>
+        <v>2.596573622781762e-09</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.583257550207833e-11</v>
+        <v>4.987136037470918e-09</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.151960636937901e-11</v>
+        <v>1.437789798330869e-08</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.936026200466401e-10</v>
+        <v>7.995057949017337e-09</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.257772854929456e-11</v>
+        <v>7.284274516905498e-09</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.479034074715948e-11</v>
+        <v>8.594673417405829e-09</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.360033197173038e-10</v>
+        <v>2.04660750569019e-08</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.139987922451404e-11</v>
+        <v>4.116922358576858e-10</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.078199057813478e-10</v>
+        <v>1.497104773484637e-09</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.572417543393989e-11</v>
+        <v>1.439975605421751e-08</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.954432697434896e-11</v>
+        <v>9.420128010972917e-10</v>
       </c>
       <c r="BO10" t="n">
-        <v>9.220853247615679e-11</v>
+        <v>1.396855076052361e-09</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.928952830798636e-11</v>
+        <v>1.195991217173287e-08</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.157526505202178e-11</v>
+        <v>6.702005617142959e-10</v>
       </c>
       <c r="BR10" t="n">
-        <v>4.166979261643888e-12</v>
+        <v>1.381974001901654e-08</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.775044521090674e-11</v>
+        <v>5.674769987251693e-09</v>
       </c>
       <c r="BT10" t="n">
-        <v>4.588491045454113e-11</v>
+        <v>7.49467776728352e-09</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.322843042385948e-11</v>
+        <v>5.200901931345925e-09</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.024653609853047e-11</v>
+        <v>1.343818389898388e-08</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.3169172110088e-11</v>
+        <v>5.457050811230602e-09</v>
       </c>
       <c r="BX10" t="n">
-        <v>1.527107260090865e-11</v>
+        <v>9.268421585773012e-10</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.226729217680301e-11</v>
+        <v>5.775231848303974e-09</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.125187608699065e-11</v>
+        <v>1.703376462103279e-08</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.660647976028613e-11</v>
+        <v>1.128555648932661e-08</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.397531825848453e-12</v>
+        <v>2.18523910078261e-09</v>
       </c>
       <c r="CC10" t="n">
-        <v>8.150497637915421e-12</v>
+        <v>2.930593101524437e-09</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.956550199633256e-11</v>
+        <v>1.342846389640329e-10</v>
       </c>
       <c r="CE10" t="n">
-        <v>6.194200707909658e-11</v>
+        <v>1.290785700547303e-08</v>
       </c>
       <c r="CF10" t="n">
-        <v>4.468751757524814e-11</v>
+        <v>6.269110230938679e-11</v>
       </c>
       <c r="CG10" t="n">
-        <v>8.957322730762662e-12</v>
+        <v>4.030707323465776e-09</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.431079213465303e-11</v>
+        <v>4.429948852191501e-09</v>
       </c>
       <c r="CI10" t="n">
-        <v>3.126901168548635e-11</v>
+        <v>9.618345231388048e-09</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.582819812717684e-11</v>
+        <v>7.23621274012487e-10</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.465899623909195e-11</v>
+        <v>6.468530600045597e-09</v>
       </c>
       <c r="CL10" t="n">
-        <v>6.518389994436546e-11</v>
+        <v>5.720611540027676e-09</v>
       </c>
       <c r="CM10" t="n">
-        <v>6.092584770023279e-11</v>
+        <v>7.817676284105346e-09</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.607688288052245e-11</v>
+        <v>1.303191687895833e-08</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.270795361302257e-11</v>
+        <v>2.252936681657047e-08</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.238523728019914e-10</v>
+        <v>1.863998910778264e-08</v>
       </c>
       <c r="CQ10" t="n">
-        <v>9.639244263892621e-11</v>
+        <v>1.182938014210322e-08</v>
       </c>
       <c r="CR10" t="n">
-        <v>2.24106740109864e-11</v>
+        <v>2.175867264142539e-09</v>
       </c>
       <c r="CS10" t="n">
-        <v>1.247692921202415e-10</v>
+        <v>1.253105175180735e-09</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.588489921879656e-11</v>
+        <v>1.42862637275698e-08</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.681994474256321e-11</v>
+        <v>1.061177279382264e-08</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.741391579546114e-11</v>
+        <v>2.429506595902353e-09</v>
       </c>
       <c r="CW10" t="n">
-        <v>5.609582937049495e-11</v>
+        <v>1.17978604663449e-08</v>
       </c>
       <c r="CX10" t="n">
-        <v>3.507175799777329e-11</v>
+        <v>2.028502921191944e-09</v>
       </c>
       <c r="CY10" t="n">
-        <v>4.626186933531784e-11</v>
+        <v>6.578377398369639e-09</v>
       </c>
       <c r="CZ10" t="n">
-        <v>3.21498730415648e-11</v>
+        <v>5.27339238942659e-09</v>
       </c>
       <c r="DA10" t="n">
-        <v>4.503294612212549e-11</v>
+        <v>1.238140878712102e-08</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.332828725858493e-11</v>
+        <v>7.624272879702687e-10</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.317906547781966e-11</v>
+        <v>6.049844181177377e-09</v>
       </c>
       <c r="DD10" t="n">
-        <v>5.960099774826588e-11</v>
+        <v>4.44268621890842e-09</v>
       </c>
       <c r="DE10" t="n">
-        <v>6.339441471769902e-11</v>
+        <v>1.813109440362837e-09</v>
       </c>
       <c r="DF10" t="n">
-        <v>7.168987625760792e-11</v>
+        <v>2.506310048389082e-09</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.539243593695616e-10</v>
+        <v>4.88897722306092e-09</v>
       </c>
       <c r="DH10" t="n">
-        <v>1.705432739473878e-10</v>
+        <v>6.035207000820719e-09</v>
       </c>
       <c r="DI10" t="n">
-        <v>3.040986906732712e-10</v>
+        <v>4.206965886766056e-09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>9.278031815052046e-11</v>
+        <v>1.795924653436032e-08</v>
       </c>
       <c r="DK10" t="n">
-        <v>1.081443129491433e-10</v>
+        <v>4.016341037527127e-09</v>
       </c>
       <c r="DL10" t="n">
-        <v>2.203591198401966e-10</v>
+        <v>1.227080481669418e-08</v>
       </c>
       <c r="DM10" t="n">
-        <v>3.916577479001759e-11</v>
+        <v>9.987035198832928e-09</v>
       </c>
       <c r="DN10" t="n">
-        <v>3.173734886008361e-11</v>
+        <v>2.065583926125214e-09</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.216107935521961e-12</v>
+        <v>5.438445249694723e-09</v>
       </c>
       <c r="DP10" t="n">
-        <v>3.99071366230519e-11</v>
+        <v>2.997958326034222e-09</v>
       </c>
       <c r="DQ10" t="n">
-        <v>1.123384371637393e-10</v>
+        <v>2.220733819058296e-09</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.630725490561982e-12</v>
+        <v>1.109483283023849e-09</v>
       </c>
       <c r="DS10" t="n">
-        <v>6.914009295644341e-12</v>
+        <v>3.800150749633247e-10</v>
       </c>
       <c r="DT10" t="n">
-        <v>1.329973457753209e-11</v>
+        <v>4.628269323347922e-09</v>
       </c>
       <c r="DU10" t="n">
-        <v>1.020850591559874e-11</v>
+        <v>1.231661261869021e-08</v>
       </c>
       <c r="DV10" t="n">
-        <v>1.165702534500213e-10</v>
+        <v>1.038556973753657e-08</v>
       </c>
       <c r="DW10" t="n">
-        <v>4.481685855761697e-11</v>
+        <v>5.625134136266752e-09</v>
       </c>
       <c r="DX10" t="n">
-        <v>2.038726826247839e-11</v>
+        <v>6.497840487895701e-09</v>
       </c>
       <c r="DY10" t="n">
-        <v>1.572043328845751e-10</v>
+        <v>1.319463649451791e-08</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.104099706967677e-11</v>
+        <v>7.920963440710693e-09</v>
       </c>
       <c r="EA10" t="n">
-        <v>1.735196361596358e-11</v>
+        <v>2.923067343729713e-10</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.739519361887432e-10</v>
+        <v>6.109619477001615e-09</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.168154974475534e-12</v>
+        <v>1.412121530819377e-09</v>
       </c>
       <c r="ED10" t="n">
-        <v>1.873299432242348e-11</v>
+        <v>1.794830772894329e-08</v>
       </c>
       <c r="EE10" t="n">
-        <v>1.385301335449229e-11</v>
+        <v>7.415590363990532e-09</v>
       </c>
       <c r="EF10" t="n">
-        <v>7.75924463569666e-13</v>
+        <v>6.250408635111171e-09</v>
       </c>
       <c r="EG10" t="n">
-        <v>6.698248899983383e-11</v>
+        <v>1.430544127600797e-09</v>
       </c>
       <c r="EH10" t="n">
-        <v>3.922768360142825e-11</v>
+        <v>4.429460354060666e-09</v>
       </c>
       <c r="EI10" t="n">
-        <v>5.582860562736158e-11</v>
+        <v>1.920574810299058e-09</v>
       </c>
       <c r="EJ10" t="n">
-        <v>4.85872696243117e-11</v>
+        <v>2.107569674336673e-09</v>
       </c>
       <c r="EK10" t="n">
-        <v>5.29695072526426e-11</v>
+        <v>6.277069974913729e-09</v>
       </c>
       <c r="EL10" t="n">
-        <v>2.421722197776255e-11</v>
+        <v>2.965699907875319e-09</v>
       </c>
       <c r="EM10" t="n">
-        <v>1.600877937157907e-11</v>
+        <v>1.003742866600987e-09</v>
       </c>
       <c r="EN10" t="n">
-        <v>5.41174570434233e-11</v>
+        <v>2.432203771718378e-09</v>
       </c>
       <c r="EO10" t="n">
-        <v>4.647265211543683e-12</v>
+        <v>1.272098093529905e-09</v>
       </c>
       <c r="EP10" t="n">
-        <v>2.138976842869234e-11</v>
+        <v>6.005250519081073e-09</v>
       </c>
       <c r="EQ10" t="n">
-        <v>3.806718829046929e-11</v>
+        <v>1.819688177917556e-09</v>
       </c>
       <c r="ER10" t="n">
-        <v>3.19674842153006e-12</v>
+        <v>1.958408768487629e-09</v>
       </c>
       <c r="ES10" t="n">
-        <v>9.883753537831552e-11</v>
+        <v>2.131627097057276e-09</v>
       </c>
       <c r="ET10" t="n">
-        <v>8.713535448734433e-11</v>
+        <v>2.94977553494391e-09</v>
       </c>
       <c r="EU10" t="n">
-        <v>2.652455338703064e-11</v>
+        <v>2.711269819766216e-10</v>
       </c>
       <c r="EV10" t="n">
-        <v>1.660461074193265e-10</v>
+        <v>5.067647634859895e-09</v>
       </c>
       <c r="EW10" t="n">
-        <v>6.129229762619204e-11</v>
+        <v>3.262706327333831e-09</v>
       </c>
       <c r="EX10" t="n">
-        <v>4.3680770805965e-12</v>
+        <v>4.346108195552034e-10</v>
       </c>
       <c r="EY10" t="n">
-        <v>5.04773688125848e-11</v>
+        <v>1.380821945673461e-08</v>
       </c>
       <c r="EZ10" t="n">
-        <v>2.744562216383528e-11</v>
+        <v>9.56646206695666e-10</v>
       </c>
       <c r="FA10" t="n">
-        <v>2.185072262017584e-11</v>
+        <v>7.388978762179477e-09</v>
       </c>
       <c r="FB10" t="n">
-        <v>2.551780488302402e-11</v>
+        <v>2.148375921606771e-09</v>
       </c>
       <c r="FC10" t="n">
-        <v>3.440428497647474e-11</v>
+        <v>7.863623530113273e-09</v>
       </c>
       <c r="FD10" t="n">
-        <v>2.225594708527012e-11</v>
+        <v>8.85795714555826e-10</v>
       </c>
       <c r="FE10" t="n">
-        <v>8.864988604306845e-12</v>
+        <v>6.586138301400979e-09</v>
       </c>
       <c r="FF10" t="n">
-        <v>6.41523431599289e-11</v>
+        <v>9.647758147934837e-10</v>
       </c>
       <c r="FG10" t="n">
-        <v>1.732641634333287e-11</v>
+        <v>6.498988569525466e-10</v>
       </c>
       <c r="FH10" t="n">
-        <v>4.768662895116016e-11</v>
+        <v>9.433634318156692e-09</v>
       </c>
       <c r="FI10" t="n">
-        <v>1.643983282839656e-10</v>
+        <v>9.315813009891372e-09</v>
       </c>
       <c r="FJ10" t="n">
-        <v>1.376522229534771e-10</v>
+        <v>8.015952346340782e-09</v>
       </c>
       <c r="FK10" t="n">
-        <v>2.387418387983509e-11</v>
+        <v>4.492338057104917e-09</v>
       </c>
       <c r="FL10" t="n">
-        <v>1.9318366351051e-11</v>
+        <v>1.493196677415654e-08</v>
       </c>
       <c r="FM10" t="n">
-        <v>5.618997888506838e-12</v>
+        <v>4.345093174151771e-09</v>
       </c>
       <c r="FN10" t="n">
-        <v>1.072499242193992e-10</v>
+        <v>8.426452424714626e-09</v>
       </c>
       <c r="FO10" t="n">
-        <v>7.326406148422393e-11</v>
+        <v>2.454717673572304e-08</v>
       </c>
       <c r="FP10" t="n">
-        <v>2.632111542610893e-12</v>
+        <v>1.354500689387805e-08</v>
       </c>
       <c r="FQ10" t="n">
-        <v>4.84525683464021e-11</v>
+        <v>1.692229467664674e-08</v>
       </c>
       <c r="FR10" t="n">
-        <v>1.177045266809174e-10</v>
+        <v>1.804272642402793e-08</v>
       </c>
       <c r="FS10" t="n">
-        <v>6.72500596876624e-11</v>
+        <v>4.436892631076716e-09</v>
       </c>
       <c r="FT10" t="n">
-        <v>1.425247142528008e-10</v>
+        <v>2.55629828416204e-09</v>
       </c>
       <c r="FU10" t="n">
-        <v>2.366778648066337e-13</v>
+        <v>2.486564287806914e-09</v>
       </c>
       <c r="FV10" t="n">
-        <v>3.516653981905371e-12</v>
+        <v>1.029552709752579e-08</v>
       </c>
       <c r="FW10" t="n">
-        <v>1.931869941795838e-11</v>
+        <v>2.313095137651544e-08</v>
       </c>
       <c r="FX10" t="n">
-        <v>1.269639168105519e-11</v>
+        <v>3.402293113907717e-09</v>
       </c>
       <c r="FY10" t="n">
-        <v>1.571074936812522e-10</v>
+        <v>4.756440130648798e-09</v>
       </c>
       <c r="FZ10" t="n">
-        <v>7.62613999727435e-11</v>
+        <v>6.795877194321065e-09</v>
       </c>
       <c r="GA10" t="n">
-        <v>1.557695292198069e-11</v>
+        <v>1.474191080319542e-08</v>
       </c>
       <c r="GB10" t="n">
-        <v>4.758055754949808e-11</v>
+        <v>1.389762749326451e-09</v>
       </c>
       <c r="GC10" t="n">
-        <v>1.621228568060573e-10</v>
+        <v>2.793368381048822e-08</v>
       </c>
       <c r="GD10" t="n">
-        <v>5.181043094548698e-11</v>
+        <v>1.766138524317284e-08</v>
       </c>
       <c r="GE10" t="n">
-        <v>1.50716314428756e-10</v>
+        <v>3.97788735284621e-09</v>
       </c>
       <c r="GF10" t="n">
-        <v>2.715943442366253e-11</v>
+        <v>1.969181706584777e-09</v>
       </c>
       <c r="GG10" t="n">
-        <v>1.087677309330459e-10</v>
+        <v>3.321592556559949e-09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0007292886730283499</v>
+        <v>2.110586501657963e-05</v>
       </c>
       <c r="B11" t="n">
-        <v>0.005123459734022617</v>
+        <v>0.005676675587892532</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0005617691203951836</v>
+        <v>0.002293933648616076</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001682058908045292</v>
+        <v>0.00244946638122201</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0008628522627986968</v>
+        <v>0.001241278136149049</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002638534875586629</v>
+        <v>0.006641334854066372</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0008118296391330659</v>
+        <v>0.0005290108383633196</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001846086466684937</v>
+        <v>0.003312443848699331</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006410356727428734</v>
+        <v>0.0008384098182432353</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001273194095119834</v>
+        <v>0.000892645854037255</v>
       </c>
       <c r="K11" t="n">
-        <v>0.004645407199859619</v>
+        <v>0.006281008943915367</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002768899721559137</v>
+        <v>0.00346904038451612</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001282320125028491</v>
+        <v>0.005184916779398918</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0001816683943616226</v>
+        <v>0.003604322206228971</v>
       </c>
       <c r="O11" t="n">
-        <v>0.00252853543497622</v>
+        <v>0.007800950668752193</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0006315773935057223</v>
+        <v>0.0004596283542923629</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0005251463735476136</v>
+        <v>0.001899220980703831</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001333543797954917</v>
+        <v>0.0005257367738522589</v>
       </c>
       <c r="S11" t="n">
-        <v>7.378643203992397e-05</v>
+        <v>0.001045878627337515</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0006662227096967399</v>
+        <v>0.0007131346501410007</v>
       </c>
       <c r="U11" t="n">
-        <v>0.000600448518525809</v>
+        <v>9.868142660707235e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>0.000342363549862057</v>
+        <v>0.0001950494188349694</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0002717728784773499</v>
+        <v>0.0009623405640013516</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0008897335501387715</v>
+        <v>0.001536731608211994</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0002858492371160537</v>
+        <v>0.001327569829300046</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0008908821037039161</v>
+        <v>0.001180053572170436</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0007156032952480018</v>
+        <v>0.0008524451404809952</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0003550783440005034</v>
+        <v>0.0003769759787246585</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0003329122555442154</v>
+        <v>0.0001422177301719785</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0002648279769346118</v>
+        <v>0.001063908799551427</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0002052374329650775</v>
+        <v>0.00167182320728898</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0007438692264258862</v>
+        <v>0.002205600030720234</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0004570510354824364</v>
+        <v>0.002036883262917399</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.00022127952252049</v>
+        <v>0.0005437524523586035</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0002790723810903728</v>
+        <v>0.00399944419041276</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0005582759040407836</v>
+        <v>0.0003286380087956786</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0007932539447210729</v>
+        <v>0.001260889694094658</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0007990208687260747</v>
+        <v>0.001043497351929545</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0001379160967189819</v>
+        <v>0.000295003002975136</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0005335143650881946</v>
+        <v>0.000614191172644496</v>
       </c>
       <c r="AO11" t="n">
-        <v>4.320943116908893e-05</v>
+        <v>0.001438971259631217</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0007443238282576203</v>
+        <v>0.001221535843797028</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0005483438144437969</v>
+        <v>0.0003678810608107597</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.184215403161943e-06</v>
+        <v>0.0005199028528295457</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0007444628281518817</v>
+        <v>9.187134855892509e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0003613356093410403</v>
+        <v>0.001142484601587057</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.003024120815098286</v>
+        <v>0.00569669296965003</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0003558190655894578</v>
+        <v>0.001872768974862993</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0005514295189641416</v>
+        <v>0.001397588639520109</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.000379265402443707</v>
+        <v>0.004595599602907896</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.002276939107105136</v>
+        <v>0.005738260224461555</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.001779517740942538</v>
+        <v>0.0001967333082575351</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0008278025779873133</v>
+        <v>0.001153010292910039</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.001452622236683965</v>
+        <v>0.0003293151094112545</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0003714853955898434</v>
+        <v>0.001509163994342089</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.0008734000148251653</v>
+        <v>0.0001371688704239205</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.001200983300805092</v>
+        <v>0.001460079336538911</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0001481899234931916</v>
+        <v>0.001584913465194404</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.0003719293745234609</v>
+        <v>0.001678535947576165</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.0003492260002531111</v>
+        <v>0.0006794978980906308</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.0004417620075400919</v>
+        <v>0.0004790413659065962</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0008282677736133337</v>
+        <v>0.002756988629698753</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.001139862346462905</v>
+        <v>0.0008730767294764519</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.0002480202238075435</v>
+        <v>0.0002336441248189658</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0005616192356683314</v>
+        <v>0.002197504043579102</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0005019110394641757</v>
+        <v>0.001149003859609365</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.975951403845102e-05</v>
+        <v>0.001141903456300497</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.952143015339971e-05</v>
+        <v>0.001626919256523252</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.000402589445002377</v>
+        <v>0.001084128976799548</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0009266518754884601</v>
+        <v>0.001020847703330219</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0006762837874703109</v>
+        <v>0.0006753965863026679</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0001240298734046519</v>
+        <v>0.001140155363827944</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0001747358473949134</v>
+        <v>0.0006972988485358655</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.001662544324062765</v>
+        <v>0.002400747966021299</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0009908167412504554</v>
+        <v>0.000239017594140023</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0001145874848589301</v>
+        <v>0.0003209623391740024</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0004851213016081601</v>
+        <v>0.0004397154552862048</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001120146363973618</v>
+        <v>0.002992242574691772</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0001715293037705123</v>
+        <v>0.00202801451086998</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0002363932144362479</v>
+        <v>0.0007029444677755237</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0004757526621688157</v>
+        <v>0.001253823167644441</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0001659290865063667</v>
+        <v>3.962541813962162e-05</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0009777088416740298</v>
+        <v>0.001717899343930185</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0004200454859528691</v>
+        <v>0.0008481636759825051</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.168030889355578e-05</v>
+        <v>0.0005620790179818869</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.000166247773449868</v>
+        <v>0.0008375730249099433</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0001302090822719038</v>
+        <v>0.00163431151304394</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0003856683906633407</v>
+        <v>9.874432726064697e-05</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0004171113250777125</v>
+        <v>0.0003737223451025784</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0003897352435160428</v>
+        <v>6.341194966807961e-05</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.001238342374563217</v>
+        <v>0.00108144071418792</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0003028986684512347</v>
+        <v>0.00110809481702745</v>
       </c>
       <c r="CO11" t="n">
-        <v>5.549154593609273e-06</v>
+        <v>0.002028474118560553</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.002117359545081854</v>
+        <v>0.001430514035746455</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0003959387831855565</v>
+        <v>0.001007202779874206</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0009039532160386443</v>
+        <v>0.0006063709734007716</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0009974397253245115</v>
+        <v>0.001736965961754322</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0005900994292460382</v>
+        <v>0.002119362121447921</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0004363940970506519</v>
+        <v>0.001023012446239591</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0001814012648537755</v>
+        <v>0.0005372907035052776</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0009133024141192436</v>
+        <v>0.001378995133563876</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0004533540923148394</v>
+        <v>0.001123611349612474</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0003702924004755914</v>
+        <v>0.0008860775269567966</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0002787742705550045</v>
+        <v>0.0009012177470140159</v>
       </c>
       <c r="DA11" t="n">
-        <v>3.769226896110922e-05</v>
+        <v>0.002172105247154832</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0004044191737193614</v>
+        <v>0.0003222394443582743</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0006362601416185498</v>
+        <v>0.0004633901407942176</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0004233723739162087</v>
+        <v>1.820569013943896e-05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0006582456408068538</v>
+        <v>0.0002149980573449284</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0002946392341982573</v>
+        <v>0.003104331903159618</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0003400929854251444</v>
+        <v>0.001815586700104177</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.0007133192848414183</v>
+        <v>0.001242166734300554</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.001248768181540072</v>
+        <v>9.433229570277035e-05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.003050933359190822</v>
+        <v>0.00208402774296701</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.000334964512148872</v>
+        <v>0.0002999292337335646</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.001268824562430382</v>
+        <v>0.002488190773874521</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.001275591901503503</v>
+        <v>0.0007226744201034307</v>
       </c>
       <c r="DN11" t="n">
-        <v>9.847852197708562e-05</v>
+        <v>0.0002713374560698867</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0004708498890977353</v>
+        <v>0.0005069110193289816</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0005263396305963397</v>
+        <v>0.0001769755326677114</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0002775792090687901</v>
+        <v>0.001127887284383178</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0004038750194013119</v>
+        <v>0.0004946844419464469</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0009483378962613642</v>
+        <v>0.001327887992374599</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.00106889265589416</v>
+        <v>0.001215510186739266</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.000663071230519563</v>
+        <v>0.001936197280883789</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0001996276841964573</v>
+        <v>0.001351915881969035</v>
       </c>
       <c r="DW11" t="n">
-        <v>4.203023854643106e-05</v>
+        <v>0.0002145704347640276</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0005794711178168654</v>
+        <v>0.0007100505754351616</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0006487024948000908</v>
+        <v>0.002289611380547285</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0008799238130450249</v>
+        <v>2.108151238644496e-05</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0003355548251420259</v>
+        <v>0.001655975007452071</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.000444849778432399</v>
+        <v>0.0001625138247618452</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0002242291520815343</v>
+        <v>0.00179164856672287</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0002966025494970381</v>
+        <v>0.001899135066196322</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.001194294658489525</v>
+        <v>0.002291562268510461</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0005415244959294796</v>
+        <v>0.0002321982756257057</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.001148856710642576</v>
+        <v>0.0001017265312839299</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0002867000002879649</v>
+        <v>0.0002193599357269704</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0001594332279637456</v>
+        <v>0.0007061408250592649</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0003129224060103297</v>
+        <v>0.0009078489383682609</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0009936337592080235</v>
+        <v>0.0004119983350392431</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0007296454859897494</v>
+        <v>0.0004399724712129682</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0001266422186745331</v>
+        <v>0.0003359327383805066</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0001391842088196427</v>
+        <v>0.001122961635701358</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0002059764228761196</v>
+        <v>0.0005915879737585783</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0005377464112825692</v>
+        <v>0.001772039337083697</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0007282043225131929</v>
+        <v>0.000745041761547327</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0004849191755056381</v>
+        <v>0.001350609818473458</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0007628772291354835</v>
+        <v>0.0003499603481031954</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0008109425543807447</v>
+        <v>0.001788385910913348</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.001282976474612951</v>
+        <v>2.99539533443749e-05</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.001456644618883729</v>
+        <v>0.0004241268616169691</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0003515787830110639</v>
+        <v>0.0004570692544803023</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.000279267318546772</v>
+        <v>0.0003904127515852451</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0008672192343510687</v>
+        <v>0.001952047343365848</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0003696900967042893</v>
+        <v>0.0006306695868261158</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0001628527097636834</v>
+        <v>0.0009984991047531366</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0002221607574028894</v>
+        <v>0.0006620584754273295</v>
       </c>
       <c r="FC11" t="n">
-        <v>3.758286766242236e-06</v>
+        <v>0.001670980011112988</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0007080914219841361</v>
+        <v>0.0001865149242803454</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0006321825785562396</v>
+        <v>0.0003470272349659353</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0005893235211260617</v>
+        <v>0.0003190629649907351</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0002081845013890415</v>
+        <v>3.200920764356852e-05</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0003622152144089341</v>
+        <v>0.0008146225591190159</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0009627366671338677</v>
+        <v>0.000842368695884943</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0008115157834254205</v>
+        <v>0.001205603708513081</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0004265916359145194</v>
+        <v>0.0002285292721353471</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.000444902922026813</v>
+        <v>0.002125473227351904</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.0004642805142793804</v>
+        <v>0.0004478693881537765</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0005309478146955371</v>
+        <v>0.001036407658830285</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0007737443083897233</v>
+        <v>0.003549343440681696</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.0007675274973735213</v>
+        <v>0.001227477798238397</v>
       </c>
       <c r="FQ11" t="n">
-        <v>3.96788127545733e-05</v>
+        <v>0.00185081351082772</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.000242158435867168</v>
+        <v>0.0002769817365333438</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0009619680931791663</v>
+        <v>0.0009086843347176909</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0002249587560072541</v>
+        <v>0.0007957561174407601</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0009084812481887639</v>
+        <v>0.0007025975501164794</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.000889189075678587</v>
+        <v>0.001457403530366719</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.000644511601421982</v>
+        <v>0.00590746384114027</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0003824589366558939</v>
+        <v>0.0005445457645691931</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.001260578166693449</v>
+        <v>0.000807690666988492</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0004752320237457752</v>
+        <v>0.0009606044040992856</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0005342074437066913</v>
+        <v>0.002824293915182352</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0002805120020639151</v>
+        <v>0.0009487284696660936</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.001013399683870375</v>
+        <v>0.002863746369257569</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0003835110692307353</v>
+        <v>0.001802513608708978</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.000817575491964817</v>
+        <v>0.0007676464738324285</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0003967010416090488</v>
+        <v>0.0005979721317999065</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0001810419344110414</v>
+        <v>0.0001074338506441563</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.02023665234446526</v>
+        <v>7.534665201092139e-05</v>
       </c>
       <c r="B12" t="n">
-        <v>0.292483925819397</v>
+        <v>0.0005576666444540024</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00708004692569375</v>
+        <v>7.226043817354366e-05</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1481190323829651</v>
+        <v>0.000266962219029665</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03883581608533859</v>
+        <v>0.0001723097084322944</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2278710603713989</v>
+        <v>0.0004957513883709908</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009451810270547867</v>
+        <v>0.0002880532410927117</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1025386825203896</v>
+        <v>0.0004255693638697267</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01339906267821789</v>
+        <v>8.628311479697004e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05653790012001991</v>
+        <v>8.906482253223658e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2734870910644531</v>
+        <v>0.0006556103471666574</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005916742607951164</v>
+        <v>4.42415512225125e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1047808080911636</v>
+        <v>0.0004180268151685596</v>
       </c>
       <c r="N12" t="n">
-        <v>0.007402054499834776</v>
+        <v>0.0003941507020499557</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2180362641811371</v>
+        <v>0.0006857254775241017</v>
       </c>
       <c r="P12" t="n">
-        <v>0.009011683985590935</v>
+        <v>0.0002050140028586611</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.04233106225728989</v>
+        <v>0.000204438591026701</v>
       </c>
       <c r="R12" t="n">
-        <v>0.008692416362464428</v>
+        <v>0.0001953012397279963</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01394344214349985</v>
+        <v>5.090924969408661e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0238085612654686</v>
+        <v>4.118708602618426e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02578062005341053</v>
+        <v>0.0001090407822630368</v>
       </c>
       <c r="V12" t="n">
-        <v>0.03893642872571945</v>
+        <v>7.305834151338786e-05</v>
       </c>
       <c r="W12" t="n">
-        <v>0.06700211018323898</v>
+        <v>9.064349433174357e-05</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02400580234825611</v>
+        <v>9.163391951005906e-05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.02178364619612694</v>
+        <v>6.288271833909675e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.06639008969068527</v>
+        <v>0.0002684000646695495</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.04126325994729996</v>
+        <v>4.241197893861681e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.004982225596904755</v>
+        <v>0.000125059625133872</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.011800785548985</v>
+        <v>8.013929618755355e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.007169472053647041</v>
+        <v>2.024113018705975e-05</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.01238104980438948</v>
+        <v>0.0001714860554784536</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.01525192707777023</v>
+        <v>0.0001393995771650225</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01654581539332867</v>
+        <v>0.0002202152245445177</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.01803364977240562</v>
+        <v>3.361756171216257e-06</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.01741924695670605</v>
+        <v>0.0004604438436217606</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.01346874423325062</v>
+        <v>6.648371345363557e-05</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.02448061481118202</v>
+        <v>9.869087080005556e-05</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.05435999855399132</v>
+        <v>5.532935756491497e-05</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.003185253590345383</v>
+        <v>0.0001239554403582588</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.009922495111823082</v>
+        <v>6.031141674611717e-05</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0008295127190649509</v>
+        <v>0.0001198409736389294</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.03444091230630875</v>
+        <v>8.363959204871207e-05</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.004564476665109396</v>
+        <v>3.791643030126579e-05</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.01689633727073669</v>
+        <v>0.0002839821972884238</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.03104422055184841</v>
+        <v>5.179366780794226e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.04319792985916138</v>
+        <v>0.000186721736099571</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2123278677463531</v>
+        <v>0.0004530744336079806</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.007510749623179436</v>
+        <v>0.000103636208223179</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0579601563513279</v>
+        <v>0.0001846690138336271</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0213102400302887</v>
+        <v>0.0004541166126728058</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.119969367980957</v>
+        <v>0.0003557270392775536</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.03461265563964844</v>
+        <v>1.596295987837948e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.02722866088151932</v>
+        <v>0.0001033476728480309</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.07038221508264542</v>
+        <v>5.128590419190004e-05</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.02555045858025551</v>
+        <v>2.467464582878165e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.04705157876014709</v>
+        <v>0.0002494638611096889</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.05751384049654007</v>
+        <v>4.750428342958912e-05</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.001180743798613548</v>
+        <v>0.0002204653865192086</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.03977224603295326</v>
+        <v>0.0002713287831284106</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.06932011991739273</v>
+        <v>7.776821439620107e-05</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.02217846736311913</v>
+        <v>0.0001042695803334936</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0240033958107233</v>
+        <v>0.0003898584109265357</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.01801223307847977</v>
+        <v>2.578301791800186e-05</v>
       </c>
       <c r="BL12" t="n">
-        <v>6.07944093644619e-05</v>
+        <v>1.744247674650978e-05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.05999037250876427</v>
+        <v>0.0001566176651977003</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.01013457030057907</v>
+        <v>1.257687290490139e-05</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01626478508114815</v>
+        <v>6.100985410739668e-05</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.004296740982681513</v>
+        <v>0.0001192022536997683</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0021707892883569</v>
+        <v>1.082958624465391e-05</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.02330923266708851</v>
+        <v>0.0003127656527794898</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.01446696370840073</v>
+        <v>0.0001382174814352766</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.01026926655322313</v>
+        <v>5.465006688609719e-05</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.01858248189091682</v>
+        <v>7.937208283692598e-05</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1120768263936043</v>
+        <v>0.0001838900498114526</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.02150421030819416</v>
+        <v>0.0001070218786480837</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.04431009665131569</v>
+        <v>0.0001270293432753533</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.02744794078171253</v>
+        <v>0.0001438798062736169</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.05089700594544411</v>
+        <v>0.0001759260630933568</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.01508958823978901</v>
+        <v>7.337889837799594e-05</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.002004137262701988</v>
+        <v>9.08596848603338e-05</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.04625633358955383</v>
+        <v>6.302618203335442e-06</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0002628173679113388</v>
+        <v>1.800347308744676e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.04009556397795677</v>
+        <v>0.0001541579549666494</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.02793374285101891</v>
+        <v>6.107004992372822e-06</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0193618256598711</v>
+        <v>9.130638500209898e-05</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.008232364431023598</v>
+        <v>7.570914021926001e-05</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.03524017333984375</v>
+        <v>0.0001640657865209505</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.02036489173769951</v>
+        <v>7.068131526466459e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.01557517237961292</v>
+        <v>1.986558891076129e-05</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.02525391988456249</v>
+        <v>5.918956594541669e-05</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.06413847208023071</v>
+        <v>4.937113408232108e-05</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.01272742636501789</v>
+        <v>0.0002526651951484382</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.00668724812567234</v>
+        <v>0.000278667634120211</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.05052947998046875</v>
+        <v>0.0003635098109953105</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.004549416713416576</v>
+        <v>1.18881871458143e-05</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.007799237035214901</v>
+        <v>0.0001584499841555953</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.05812123417854309</v>
+        <v>6.294358900049701e-05</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.05391817539930344</v>
+        <v>0.0001448770490242168</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.01043883431702852</v>
+        <v>0.0001140822569141164</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.0009416760876774788</v>
+        <v>4.393059134599753e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.03571484610438347</v>
+        <v>0.0001403768837917596</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.02421785518527031</v>
+        <v>1.461784222556162e-07</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0353582426905632</v>
+        <v>0.0001221128040924668</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0107139041647315</v>
+        <v>5.167398194316775e-05</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.03668152168393135</v>
+        <v>0.0001857460592873394</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.02125009894371033</v>
+        <v>1.354455434920965e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.02972018532454967</v>
+        <v>6.652798219874967e-06</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.01393593475222588</v>
+        <v>2.273699283250608e-05</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.008743803948163986</v>
+        <v>6.404426676454023e-05</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.01422584056854248</v>
+        <v>6.493827095255256e-05</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.009145039133727551</v>
+        <v>0.0001894192537292838</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1083380952477455</v>
+        <v>6.811545608798042e-05</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05626196786761284</v>
+        <v>0.0004130098968744278</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.03664886578917503</v>
+        <v>0.0001364727795589715</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0003624125383794308</v>
+        <v>7.568365253973752e-05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0464673638343811</v>
+        <v>0.0002460089162923396</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.02717494778335094</v>
+        <v>0.0001168984599644318</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.004652342293411493</v>
+        <v>7.64687720220536e-05</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0008728886023163795</v>
+        <v>0.0001253829395864159</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.02266917936503887</v>
+        <v>8.17667823866941e-05</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.001039465889334679</v>
+        <v>9.521413448965177e-05</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.005997548811137676</v>
+        <v>1.343372059636749e-05</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.008676251396536827</v>
+        <v>9.4499964689021e-06</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.002582381013780832</v>
+        <v>0.0001213371797348373</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.00330926850438118</v>
+        <v>0.0002812955062836409</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.02385660074651241</v>
+        <v>6.935997225809842e-05</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0007070107385516167</v>
+        <v>6.528028461616486e-05</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.03260188922286034</v>
+        <v>8.306747622555122e-05</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.02572822384536266</v>
+        <v>1.157809492724482e-06</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.01183806359767914</v>
+        <v>0.0002092532231472433</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.002768405247479677</v>
+        <v>0.0001907062687678263</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.01771574653685093</v>
+        <v>8.62476445036009e-05</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.002267822623252869</v>
+        <v>1.691512443358079e-05</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.003897102084010839</v>
+        <v>8.392377640120685e-05</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.01626854762434959</v>
+        <v>0.0002663755149114877</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0177092682570219</v>
+        <v>7.179869044193765e-06</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.04576597362756729</v>
+        <v>3.84698978450615e-05</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.01463432516902685</v>
+        <v>6.069092341931537e-05</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01107825711369514</v>
+        <v>1.854522997746244e-05</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.003351270221173763</v>
+        <v>7.017249299678952e-05</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.02215087972581387</v>
+        <v>0.0002036009827861562</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.02014325000345707</v>
+        <v>7.315113907679915e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.008368423208594322</v>
+        <v>7.017305961198872e-06</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0127155464142561</v>
+        <v>3.504216874716803e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0004197601228952408</v>
+        <v>4.79623704450205e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.02099652588367462</v>
+        <v>8.23005975689739e-05</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.02553407661616802</v>
+        <v>0.0001343863550573587</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02960816398262978</v>
+        <v>0.0001055175744113512</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01975108310580254</v>
+        <v>4.633619755622931e-05</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.03215945512056351</v>
+        <v>0.0001414238213328645</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.05010540038347244</v>
+        <v>7.387626828858629e-05</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.08045644313097</v>
+        <v>1.91890612768475e-05</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.008311638608574867</v>
+        <v>0.0001125578710343689</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.006566582713276148</v>
+        <v>4.816601358470507e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.03411320224404335</v>
+        <v>0.0002050547627732158</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.01974849216639996</v>
+        <v>1.059525402524741e-06</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.02349472418427467</v>
+        <v>0.0001582198892720044</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.00770418718457222</v>
+        <v>4.600388274411671e-05</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.03052231669425964</v>
+        <v>0.0001600273681106046</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.03587422892451286</v>
+        <v>5.3911058785161e-05</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.02098602429032326</v>
+        <v>9.659115676186047e-07</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.02619985491037369</v>
+        <v>4.751405867864378e-06</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.01223727501928806</v>
+        <v>3.094939893344417e-05</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01259662676602602</v>
+        <v>0.0002150612272089347</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.02567204274237156</v>
+        <v>0.0001922720111906528</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.04128187149763107</v>
+        <v>8.973792137112468e-05</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.008640616200864315</v>
+        <v>0.0001440839696442708</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.01895955577492714</v>
+        <v>0.0001054538297466934</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.002317844424396753</v>
+        <v>0.0001108450887841173</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.02321543544530869</v>
+        <v>0.0001574684429215267</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0205408725887537</v>
+        <v>0.0002202050527557731</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0225664246827364</v>
+        <v>0.0001202642306452617</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.04575827717781067</v>
+        <v>5.258404780761339e-05</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.03729543834924698</v>
+        <v>0.0003679635701701045</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01037292089313269</v>
+        <v>0.0001386669464409351</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.005012751556932926</v>
+        <v>0.0002657397708389908</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01237049698829651</v>
+        <v>5.152887024451047e-05</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.03562486916780472</v>
+        <v>2.819414658006281e-05</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.006678466219455004</v>
+        <v>0.0001601911790203303</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.01782098785042763</v>
+        <v>0.0001392734120599926</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.05956649035215378</v>
+        <v>2.178107752115466e-05</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.01710194535553455</v>
+        <v>0.0002163868048228323</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.03143071383237839</v>
+        <v>0.0002044002321781591</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.01636368595063686</v>
+        <v>4.077413905179128e-05</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.01384407468140125</v>
+        <v>0.0002918321697507054</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.02384742721915245</v>
+        <v>0.0002643350453581661</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.1185244619846344</v>
+        <v>4.487401020014659e-05</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.002317036502063274</v>
+        <v>7.839269528631121e-05</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.009340224787592888</v>
+        <v>7.073197048157454e-05</v>
       </c>
     </row>
     <row r="13">
@@ -8396,571 +8396,571 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.138248939649202e-05</v>
+        <v>7.554626790806651e-06</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0004674282972700894</v>
+        <v>0.0002754486631602049</v>
       </c>
       <c r="C15" t="n">
-        <v>1.84515356522752e-05</v>
+        <v>5.502663407241926e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>9.859175042947754e-05</v>
+        <v>0.0001462165964767337</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0001134976846515201</v>
+        <v>0.0001399179018335417</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0001523977553006262</v>
+        <v>0.0003619908238761127</v>
       </c>
       <c r="G15" t="n">
-        <v>7.015273877186701e-05</v>
+        <v>0.0001706143957562745</v>
       </c>
       <c r="H15" t="n">
-        <v>7.044524681987241e-05</v>
+        <v>0.0002385539701208472</v>
       </c>
       <c r="I15" t="n">
-        <v>8.509832696290687e-05</v>
+        <v>7.239920523716137e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>4.640034239855595e-05</v>
+        <v>2.291123564646114e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0004271079087629914</v>
+        <v>0.0003664773248601705</v>
       </c>
       <c r="L15" t="n">
-        <v>4.93716606797534e-06</v>
+        <v>4.237943721818738e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>6.537375884363428e-05</v>
+        <v>0.0002207380603067577</v>
       </c>
       <c r="N15" t="n">
-        <v>1.500888356531505e-05</v>
+        <v>0.0003150733537040651</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0001145301430369727</v>
+        <v>0.0004802141047548503</v>
       </c>
       <c r="P15" t="n">
-        <v>3.704111077240668e-05</v>
+        <v>0.0001079137000488117</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.368117566220462e-05</v>
+        <v>0.000112999026896432</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0001022789947455749</v>
+        <v>9.193950245389715e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>1.647205499466509e-05</v>
+        <v>2.754998422460631e-05</v>
       </c>
       <c r="T15" t="n">
-        <v>4.795105633093044e-05</v>
+        <v>1.290384534513578e-05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.106344825529959e-05</v>
+        <v>6.247054261621088e-05</v>
       </c>
       <c r="V15" t="n">
-        <v>3.247761924285442e-05</v>
+        <v>2.748030055954587e-05</v>
       </c>
       <c r="W15" t="n">
-        <v>5.132056685397401e-05</v>
+        <v>3.262343670940027e-05</v>
       </c>
       <c r="X15" t="n">
-        <v>2.091487476718612e-05</v>
+        <v>5.846372368978336e-05</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.27486689761281e-06</v>
+        <v>5.582731319009326e-05</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.26104442239739e-05</v>
+        <v>0.0001744499459164217</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.532338450895622e-05</v>
+        <v>2.412694630038459e-05</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.57317621819675e-05</v>
+        <v>3.89712986361701e-05</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.900178489857353e-05</v>
+        <v>1.308294667978771e-05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.492733645136468e-06</v>
+        <v>9.894029062706977e-06</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.117851545335725e-05</v>
+        <v>7.503878441639245e-05</v>
       </c>
       <c r="AF15" t="n">
-        <v>8.823926691547967e-06</v>
+        <v>0.0001311883970629424</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.130541113525396e-05</v>
+        <v>7.280467980308458e-05</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.289843658014433e-05</v>
+        <v>1.861169766925741e-05</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.258235624845838e-05</v>
+        <v>0.0002379000652581453</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.621904084458947e-05</v>
+        <v>2.509978367015719e-05</v>
       </c>
       <c r="AK15" t="n">
-        <v>7.208008173620328e-05</v>
+        <v>2.176910129492171e-05</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.364281267044134e-05</v>
+        <v>1.569565938552842e-05</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.680937748460565e-05</v>
+        <v>1.532400347059593e-06</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.672427919809707e-05</v>
+        <v>2.400308403593954e-05</v>
       </c>
       <c r="AO15" t="n">
-        <v>3.540526449796744e-05</v>
+        <v>5.998814958729781e-05</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.283255864516832e-05</v>
+        <v>5.790322393295355e-05</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.189086419297382e-05</v>
+        <v>3.084833224420436e-05</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.655404376942897e-06</v>
+        <v>0.0001664635929046199</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.105169162154198e-05</v>
+        <v>3.282420038885903e-06</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.324645361630246e-06</v>
+        <v>5.925600999034941e-05</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.000269425188889727</v>
+        <v>0.000348402390955016</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.745617479784414e-05</v>
+        <v>1.377148146275431e-05</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.099163612001576e-05</v>
+        <v>4.188874299870804e-05</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.813910603232216e-05</v>
+        <v>0.0001759891893016174</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.587333336938173e-05</v>
+        <v>0.0002788131241686642</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.000108918291516602</v>
+        <v>1.867568789748475e-05</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.516376818879507e-05</v>
+        <v>7.349184306804091e-05</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.094075484317727e-05</v>
+        <v>3.768634633161128e-05</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.504552973434329e-06</v>
+        <v>2.49532240559347e-06</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.125848009716719e-05</v>
+        <v>8.923991117626429e-05</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.616265793330967e-05</v>
+        <v>2.859854430425912e-05</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.388024222454987e-05</v>
+        <v>0.0001468786940677091</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.753930549370125e-05</v>
+        <v>9.086499630939215e-05</v>
       </c>
       <c r="BH15" t="n">
-        <v>6.391495844582096e-05</v>
+        <v>3.430104334256612e-05</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.285942198592238e-05</v>
+        <v>5.001942554372363e-05</v>
       </c>
       <c r="BJ15" t="n">
-        <v>4.329023795435205e-05</v>
+        <v>0.0001973840116988868</v>
       </c>
       <c r="BK15" t="n">
-        <v>8.994501695269719e-05</v>
+        <v>5.829126166645437e-05</v>
       </c>
       <c r="BL15" t="n">
-        <v>2.400615812803153e-05</v>
+        <v>8.061375410761684e-06</v>
       </c>
       <c r="BM15" t="n">
-        <v>5.321974094840698e-05</v>
+        <v>0.0001190886541735381</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.189045906357933e-05</v>
+        <v>5.150572178536095e-06</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.611793570395093e-05</v>
+        <v>8.577387052355334e-05</v>
       </c>
       <c r="BP15" t="n">
-        <v>2.094975207000971e-05</v>
+        <v>8.214979607146233e-05</v>
       </c>
       <c r="BQ15" t="n">
-        <v>2.528547156543937e-06</v>
+        <v>2.8553748052218e-05</v>
       </c>
       <c r="BR15" t="n">
-        <v>3.189599374309182e-05</v>
+        <v>0.0001332530373474583</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.262952749442775e-06</v>
+        <v>7.032876601442695e-05</v>
       </c>
       <c r="BT15" t="n">
-        <v>1.226696986122988e-05</v>
+        <v>6.742315599694848e-05</v>
       </c>
       <c r="BU15" t="n">
-        <v>8.889940545486752e-06</v>
+        <v>1.204423188028159e-05</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0001623938733246177</v>
+        <v>0.0001661050628172234</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.979682929231785e-05</v>
+        <v>2.74775975412922e-05</v>
       </c>
       <c r="BX15" t="n">
-        <v>2.190635859733447e-05</v>
+        <v>8.158424316206947e-05</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.934121246449649e-05</v>
+        <v>4.699729470303282e-05</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.399740449414821e-05</v>
+        <v>0.0001262191362911835</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.388095734000672e-05</v>
+        <v>2.806710290315095e-05</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.434243237483315e-06</v>
+        <v>7.043380901450291e-05</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.665482886892278e-05</v>
+        <v>4.12250665249303e-06</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.151394801330753e-05</v>
+        <v>2.085928645101376e-05</v>
       </c>
       <c r="CE15" t="n">
-        <v>7.83202558523044e-05</v>
+        <v>6.928546645212919e-05</v>
       </c>
       <c r="CF15" t="n">
-        <v>1.510391120973509e-05</v>
+        <v>4.46761578132282e-06</v>
       </c>
       <c r="CG15" t="n">
-        <v>9.343822057417128e-06</v>
+        <v>6.235251203179359e-05</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.680721106822602e-05</v>
+        <v>4.705650280811824e-05</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.100118333852151e-05</v>
+        <v>0.0001075120308087207</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.88691844616551e-05</v>
+        <v>4.456216265680268e-05</v>
       </c>
       <c r="CK15" t="n">
-        <v>8.916804290493019e-06</v>
+        <v>1.008114850264974e-05</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.067757304757833e-05</v>
+        <v>2.736132228164934e-05</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0001113506004912779</v>
+        <v>4.308718416723423e-05</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.163501812901814e-05</v>
+        <v>0.000191124840057455</v>
       </c>
       <c r="CO15" t="n">
-        <v>2.510461490601301e-05</v>
+        <v>0.0001006840320769697</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0001419416221324354</v>
+        <v>0.0001900326169561595</v>
       </c>
       <c r="CQ15" t="n">
-        <v>6.459512951551005e-05</v>
+        <v>1.130203418142628e-05</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0001039735288941301</v>
+        <v>0.000100678123999387</v>
       </c>
       <c r="CS15" t="n">
-        <v>7.676190580241382e-05</v>
+        <v>3.709238080773503e-05</v>
       </c>
       <c r="CT15" t="n">
-        <v>4.987229476682842e-05</v>
+        <v>5.919846080360003e-05</v>
       </c>
       <c r="CU15" t="n">
-        <v>4.830526086152531e-05</v>
+        <v>2.648674853844568e-05</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.927273842738941e-05</v>
+        <v>6.088473128329497e-06</v>
       </c>
       <c r="CW15" t="n">
-        <v>7.349321822402999e-05</v>
+        <v>6.437175034079701e-05</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.358524241368286e-05</v>
+        <v>4.264413291821256e-06</v>
       </c>
       <c r="CY15" t="n">
-        <v>3.125383955193684e-05</v>
+        <v>8.054561476456001e-05</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.281538218085188e-05</v>
+        <v>4.039100531372242e-05</v>
       </c>
       <c r="DA15" t="n">
-        <v>3.101386937487405e-06</v>
+        <v>0.0001276787661481649</v>
       </c>
       <c r="DB15" t="n">
-        <v>2.803410097840242e-05</v>
+        <v>9.229500392393675e-06</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.305348061781842e-05</v>
+        <v>8.725637599127367e-07</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.246443909825757e-05</v>
+        <v>1.56251153384801e-05</v>
       </c>
       <c r="DE15" t="n">
-        <v>3.806266977335326e-05</v>
+        <v>3.451423935985076e-06</v>
       </c>
       <c r="DF15" t="n">
-        <v>6.482492608483881e-05</v>
+        <v>0.0001622140989638865</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.800751462928019e-05</v>
+        <v>8.418591460213065e-05</v>
       </c>
       <c r="DH15" t="n">
-        <v>5.081366543890908e-05</v>
+        <v>1.822809099394362e-05</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0001389850658597425</v>
+        <v>0.0001754132972564548</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.0001871412241598591</v>
+        <v>0.0001100195731851272</v>
       </c>
       <c r="DK15" t="n">
-        <v>2.279365071444772e-05</v>
+        <v>1.532948590465821e-05</v>
       </c>
       <c r="DL15" t="n">
-        <v>3.193409065715969e-05</v>
+        <v>8.922476990846917e-05</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0001138390289270319</v>
+        <v>2.484361175447702e-05</v>
       </c>
       <c r="DN15" t="n">
-        <v>2.644493179104757e-05</v>
+        <v>2.362649138376582e-05</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.018881787080318e-05</v>
+        <v>3.662891685962677e-06</v>
       </c>
       <c r="DP15" t="n">
-        <v>4.188345337752253e-05</v>
+        <v>2.995444447151385e-05</v>
       </c>
       <c r="DQ15" t="n">
-        <v>4.189364335616119e-05</v>
+        <v>3.965227006119676e-05</v>
       </c>
       <c r="DR15" t="n">
-        <v>2.828208198479842e-05</v>
+        <v>1.270416760235094e-06</v>
       </c>
       <c r="DS15" t="n">
-        <v>1.60346880875295e-05</v>
+        <v>2.244535153295146e-06</v>
       </c>
       <c r="DT15" t="n">
-        <v>7.034729060251266e-05</v>
+        <v>7.32435510144569e-05</v>
       </c>
       <c r="DU15" t="n">
-        <v>3.411257421248592e-05</v>
+        <v>0.0001454723824281245</v>
       </c>
       <c r="DV15" t="n">
-        <v>4.169124804320745e-05</v>
+        <v>3.20238177664578e-05</v>
       </c>
       <c r="DW15" t="n">
-        <v>1.016414807963884e-05</v>
+        <v>2.696034243854228e-05</v>
       </c>
       <c r="DX15" t="n">
-        <v>6.174589361762628e-05</v>
+        <v>3.486333298496902e-05</v>
       </c>
       <c r="DY15" t="n">
-        <v>3.384593583177775e-06</v>
+        <v>9.33820592763368e-06</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.209306593518704e-05</v>
+        <v>0.0001294227840844542</v>
       </c>
       <c r="EA15" t="n">
-        <v>5.170873555471189e-05</v>
+        <v>7.662392454221845e-05</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.430867971270345e-05</v>
+        <v>6.412101356545463e-05</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.27323619381059e-05</v>
+        <v>7.897247996879742e-06</v>
       </c>
       <c r="ED15" t="n">
-        <v>4.549039294943213e-05</v>
+        <v>7.085907418513671e-05</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.0001002780991257168</v>
+        <v>0.0001471258292440325</v>
       </c>
       <c r="EF15" t="n">
-        <v>6.047507849871181e-05</v>
+        <v>2.351045986870304e-05</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0001104419061448425</v>
+        <v>2.378770295763388e-05</v>
       </c>
       <c r="EH15" t="n">
-        <v>6.423737886507297e-06</v>
+        <v>4.419573815539479e-05</v>
       </c>
       <c r="EI15" t="n">
-        <v>9.234645403921604e-08</v>
+        <v>1.505102409282699e-05</v>
       </c>
       <c r="EJ15" t="n">
-        <v>5.315057023835834e-06</v>
+        <v>4.082029772689566e-05</v>
       </c>
       <c r="EK15" t="n">
-        <v>5.623965989798307e-05</v>
+        <v>0.0001148322044173256</v>
       </c>
       <c r="EL15" t="n">
-        <v>4.290399738238193e-05</v>
+        <v>5.689729732694104e-05</v>
       </c>
       <c r="EM15" t="n">
-        <v>2.263922215206549e-05</v>
+        <v>2.565561590017751e-05</v>
       </c>
       <c r="EN15" t="n">
-        <v>1.14161830424564e-05</v>
+        <v>6.913182915013749e-06</v>
       </c>
       <c r="EO15" t="n">
-        <v>2.445992868160829e-05</v>
+        <v>1.477954356232658e-06</v>
       </c>
       <c r="EP15" t="n">
-        <v>2.717870665946975e-05</v>
+        <v>8.180093573173508e-05</v>
       </c>
       <c r="EQ15" t="n">
-        <v>1.883559161797166e-05</v>
+        <v>5.738369509344921e-05</v>
       </c>
       <c r="ER15" t="n">
-        <v>4.53014399681706e-05</v>
+        <v>8.227476791944355e-05</v>
       </c>
       <c r="ES15" t="n">
-        <v>4.921059735352173e-05</v>
+        <v>1.98731850105105e-05</v>
       </c>
       <c r="ET15" t="n">
-        <v>8.794484529062174e-06</v>
+        <v>7.29490420781076e-05</v>
       </c>
       <c r="EU15" t="n">
-        <v>8.867942960932851e-05</v>
+        <v>4.072104638908058e-05</v>
       </c>
       <c r="EV15" t="n">
-        <v>6.772939377697185e-05</v>
+        <v>2.06279510166496e-05</v>
       </c>
       <c r="EW15" t="n">
-        <v>2.123968079104088e-05</v>
+        <v>5.794341996079311e-05</v>
       </c>
       <c r="EX15" t="n">
-        <v>2.517086613806896e-05</v>
+        <v>1.358070448986837e-06</v>
       </c>
       <c r="EY15" t="n">
-        <v>7.643481512786821e-05</v>
+        <v>0.0001034770830301568</v>
       </c>
       <c r="EZ15" t="n">
-        <v>8.976453500508796e-06</v>
+        <v>1.326303572568577e-05</v>
       </c>
       <c r="FA15" t="n">
-        <v>8.681041435920633e-06</v>
+        <v>9.245890396414325e-05</v>
       </c>
       <c r="FB15" t="n">
-        <v>1.219377736561e-05</v>
+        <v>3.167131944792345e-05</v>
       </c>
       <c r="FC15" t="n">
-        <v>4.172457920503803e-06</v>
+        <v>0.0001064886600943282</v>
       </c>
       <c r="FD15" t="n">
-        <v>4.493529195315205e-05</v>
+        <v>3.522800034261309e-05</v>
       </c>
       <c r="FE15" t="n">
-        <v>1.91099079529522e-05</v>
+        <v>2.761864834610606e-06</v>
       </c>
       <c r="FF15" t="n">
-        <v>3.675408515846357e-05</v>
+        <v>1.399952793690318e-06</v>
       </c>
       <c r="FG15" t="n">
-        <v>2.429770756862126e-05</v>
+        <v>7.806635039742105e-06</v>
       </c>
       <c r="FH15" t="n">
-        <v>2.262846101075411e-05</v>
+        <v>0.0001109946315409616</v>
       </c>
       <c r="FI15" t="n">
-        <v>2.687172309379093e-05</v>
+        <v>7.133724284358323e-05</v>
       </c>
       <c r="FJ15" t="n">
-        <v>6.81323726894334e-05</v>
+        <v>3.42834900948219e-05</v>
       </c>
       <c r="FK15" t="n">
-        <v>2.893361306632869e-05</v>
+        <v>9.000054706120864e-05</v>
       </c>
       <c r="FL15" t="n">
-        <v>1.242128928424791e-05</v>
+        <v>8.756159513723105e-05</v>
       </c>
       <c r="FM15" t="n">
-        <v>3.784141517826356e-05</v>
+        <v>8.29803102533333e-05</v>
       </c>
       <c r="FN15" t="n">
-        <v>1.553362562844995e-05</v>
+        <v>4.91024911752902e-05</v>
       </c>
       <c r="FO15" t="n">
-        <v>3.699460285133682e-05</v>
+        <v>0.0001022881624521688</v>
       </c>
       <c r="FP15" t="n">
-        <v>6.940004823263735e-05</v>
+        <v>1.408884418196976e-05</v>
       </c>
       <c r="FQ15" t="n">
-        <v>2.840687193383928e-05</v>
+        <v>4.471472493605688e-06</v>
       </c>
       <c r="FR15" t="n">
-        <v>4.778662696480751e-05</v>
+        <v>0.0001684341405052692</v>
       </c>
       <c r="FS15" t="n">
-        <v>7.616729271830991e-05</v>
+        <v>9.002887236420065e-05</v>
       </c>
       <c r="FT15" t="n">
-        <v>1.764171611284837e-05</v>
+        <v>0.0002108096668962389</v>
       </c>
       <c r="FU15" t="n">
-        <v>6.488937651738524e-05</v>
+        <v>4.371036629891023e-05</v>
       </c>
       <c r="FV15" t="n">
-        <v>1.515650728833862e-05</v>
+        <v>3.06300753436517e-05</v>
       </c>
       <c r="FW15" t="n">
-        <v>9.527648217044771e-06</v>
+        <v>0.0001288376952288672</v>
       </c>
       <c r="FX15" t="n">
-        <v>2.617268728499766e-05</v>
+        <v>6.702392420265824e-05</v>
       </c>
       <c r="FY15" t="n">
-        <v>7.362080941675231e-05</v>
+        <v>5.621531454380602e-05</v>
       </c>
       <c r="FZ15" t="n">
-        <v>2.709897307795472e-05</v>
+        <v>9.877094998955727e-05</v>
       </c>
       <c r="GA15" t="n">
-        <v>1.115941995522007e-05</v>
+        <v>9.334144851891324e-05</v>
       </c>
       <c r="GB15" t="n">
-        <v>7.540901151514845e-06</v>
+        <v>1.525282459624577e-05</v>
       </c>
       <c r="GC15" t="n">
-        <v>1.209079346153885e-05</v>
+        <v>0.000173146981978789</v>
       </c>
       <c r="GD15" t="n">
-        <v>4.344449553173035e-05</v>
+        <v>0.000145695245009847</v>
       </c>
       <c r="GE15" t="n">
-        <v>9.199593478115276e-07</v>
+        <v>8.853967301547527e-07</v>
       </c>
       <c r="GF15" t="n">
-        <v>4.217899913783185e-05</v>
+        <v>8.099256956484169e-05</v>
       </c>
       <c r="GG15" t="n">
-        <v>2.132562076440081e-05</v>
+        <v>6.466444756370038e-05</v>
       </c>
     </row>
   </sheetData>
